--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Bàsquet Girona.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Bàsquet Girona.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2185.96</v>
+        <v>2499.08</v>
       </c>
       <c r="C2" t="n">
-        <v>2190.82</v>
+        <v>2503.6</v>
       </c>
       <c r="D2" t="n">
-        <v>111.1912434613524</v>
+        <v>109.8817702508388</v>
       </c>
       <c r="E2" t="n">
-        <v>115.0254242703645</v>
+        <v>114.2754433615594</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5357334766254702</v>
+        <v>0.5281293952180028</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1534796719372012</v>
+        <v>0.1596069505357242</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3062015503875969</v>
+        <v>0.3189009159034138</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2375067168189146</v>
+        <v>0.2334739803094233</v>
       </c>
       <c r="J2" t="n">
-        <v>292</v>
+        <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>293</v>
+        <v>360</v>
       </c>
       <c r="L2" t="n">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="M2" t="n">
-        <v>365</v>
+        <v>438</v>
       </c>
       <c r="N2" t="n">
-        <v>688</v>
+        <v>785</v>
       </c>
       <c r="O2" t="n">
-        <v>899</v>
+        <v>1033</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4830736163353036</v>
+        <v>0.4842944210032817</v>
       </c>
       <c r="Q2" t="n">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="R2" t="n">
-        <v>353</v>
+        <v>408</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1896829661472327</v>
+        <v>0.1912798874824191</v>
       </c>
       <c r="T2" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="U2" t="n">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1579795808704997</v>
+        <v>0.1504922644163151</v>
       </c>
       <c r="W2" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="X2" t="n">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09188608275120903</v>
+        <v>0.0923581809657759</v>
       </c>
       <c r="Z2" t="n">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="AA2" t="n">
-        <v>728</v>
+        <v>831</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3911875335840946</v>
+        <v>0.3895921237693389</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7652947719688543</v>
+        <v>0.7599225556631172</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.481586402266289</v>
+        <v>0.4754901960784313</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3945578231292517</v>
+        <v>0.3800623052959501</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3705583756345178</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3392857142857143</v>
+        <v>0.332129963898917</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.530589543937709</v>
+        <v>1.519845111326234</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7891156462585034</v>
+        <v>0.7601246105919003</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.03448275862069</v>
+        <v>1.018482490272373</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7913279132791328</v>
+        <v>0.7465116279069768</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.9272151898734177</v>
+        <v>0.9399477806788512</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.686274509803922</v>
+        <v>1.727272727272727</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.346354166666667</v>
+        <v>1.263043478260869</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.846354166666667</v>
+        <v>4.636956521739131</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.192708333333333</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.07000000000001</v>
+        <v>78.09625</v>
       </c>
       <c r="C3" t="n">
-        <v>78.24357142857141</v>
+        <v>78.2375</v>
       </c>
       <c r="D3" t="n">
-        <v>111.1912434613524</v>
+        <v>109.8817702508388</v>
       </c>
       <c r="E3" t="n">
-        <v>115.0254242703645</v>
+        <v>114.2754433615594</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5357334766254703</v>
+        <v>0.5281293952180028</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1534796719372012</v>
+        <v>0.1596069505357242</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3062015503875969</v>
+        <v>0.3189009159034138</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2375067168189146</v>
+        <v>0.2334739803094233</v>
       </c>
       <c r="J3" t="n">
-        <v>10.42857142857143</v>
+        <v>10.03125</v>
       </c>
       <c r="K3" t="n">
-        <v>10.46428571428571</v>
+        <v>11.25</v>
       </c>
       <c r="L3" t="n">
-        <v>6.142857142857143</v>
+        <v>5.9375</v>
       </c>
       <c r="M3" t="n">
-        <v>13.03571428571429</v>
+        <v>13.6875</v>
       </c>
       <c r="N3" t="n">
-        <v>24.57142857142857</v>
+        <v>24.53125</v>
       </c>
       <c r="O3" t="n">
-        <v>32.10714285714285</v>
+        <v>32.28125</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4830736163353036</v>
+        <v>0.4842944210032817</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.071428571428571</v>
+        <v>6.0625</v>
       </c>
       <c r="R3" t="n">
-        <v>12.60714285714286</v>
+        <v>12.75</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1896829661472327</v>
+        <v>0.1912798874824191</v>
       </c>
       <c r="T3" t="n">
-        <v>4.142857142857143</v>
+        <v>3.8125</v>
       </c>
       <c r="U3" t="n">
-        <v>10.5</v>
+        <v>10.03125</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1579795808704997</v>
+        <v>0.1504922644163151</v>
       </c>
       <c r="W3" t="n">
-        <v>2.25</v>
+        <v>2.28125</v>
       </c>
       <c r="X3" t="n">
-        <v>6.107142857142857</v>
+        <v>6.15625</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09188608275120903</v>
+        <v>0.0923581809657759</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.821428571428571</v>
+        <v>8.625</v>
       </c>
       <c r="AA3" t="n">
-        <v>26</v>
+        <v>25.96875</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3911875335840946</v>
+        <v>0.3895921237693389</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7652947719688544</v>
+        <v>0.7599225556631172</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4815864022662889</v>
+        <v>0.4754901960784313</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3945578231292518</v>
+        <v>0.3800623052959501</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.368421052631579</v>
+        <v>0.3705583756345178</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3392857142857143</v>
+        <v>0.332129963898917</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.530589543937709</v>
+        <v>1.519845111326234</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7891156462585035</v>
+        <v>0.7601246105919003</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.03448275862069</v>
+        <v>1.018482490272373</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7913279132791328</v>
+        <v>0.7465116279069768</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9272151898734176</v>
+        <v>0.9399477806788512</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.686274509803922</v>
+        <v>1.727272727272727</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.346354166666667</v>
+        <v>1.263043478260869</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.846354166666666</v>
+        <v>4.636956521739131</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.192708333333333</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2195.68</v>
+        <v>2508.12</v>
       </c>
       <c r="C4" t="n">
-        <v>2190.82</v>
+        <v>2503.6</v>
       </c>
       <c r="D4" t="n">
-        <v>115.0254242703645</v>
+        <v>114.2754433615594</v>
       </c>
       <c r="E4" t="n">
-        <v>111.1912434613524</v>
+        <v>109.8817702508388</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5365384615384615</v>
+        <v>0.5340086830680174</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1472066637943415</v>
+        <v>0.1500809739208131</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3025291828793774</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3115384615384615</v>
+        <v>0.3121080559575494</v>
       </c>
       <c r="J4" t="n">
-        <v>336</v>
+        <v>401</v>
       </c>
       <c r="K4" t="n">
-        <v>305</v>
+        <v>351</v>
       </c>
       <c r="L4" t="n">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="M4" t="n">
-        <v>343</v>
+        <v>399</v>
       </c>
       <c r="N4" t="n">
-        <v>818</v>
+        <v>936</v>
       </c>
       <c r="O4" t="n">
-        <v>1045</v>
+        <v>1198</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5741758241758241</v>
+        <v>0.5779064158224795</v>
       </c>
       <c r="Q4" t="n">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="R4" t="n">
-        <v>375</v>
+        <v>426</v>
       </c>
       <c r="S4" t="n">
-        <v>0.206043956043956</v>
+        <v>0.2054992764109985</v>
       </c>
       <c r="T4" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="U4" t="n">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1291208791208791</v>
+        <v>0.1249397009165461</v>
       </c>
       <c r="W4" t="n">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="X4" t="n">
-        <v>239</v>
+        <v>285</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1313186813186813</v>
+        <v>0.1374819102749638</v>
       </c>
       <c r="Z4" t="n">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="AA4" t="n">
-        <v>648</v>
+        <v>728</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3560439560439561</v>
+        <v>0.3511818620356971</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7827751196172249</v>
+        <v>0.7813021702838063</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4533333333333333</v>
+        <v>0.4530516431924883</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3531914893617021</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3430962343096234</v>
+        <v>0.3473684210526316</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3595679012345679</v>
+        <v>0.353021978021978</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.56555023923445</v>
+        <v>1.562604340567613</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.7063829787234043</v>
+        <v>0.7027027027027027</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.065388951521984</v>
+        <v>1.054294175715696</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.875</v>
+        <v>0.8717391304347826</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.9807073954983923</v>
+        <v>0.9831932773109243</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.521367521367521</v>
+        <v>1.511627906976744</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.376693766937669</v>
+        <v>1.348837209302326</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.932249322493225</v>
+        <v>4.82093023255814</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.308943089430894</v>
+        <v>6.169767441860465</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78.41714285714285</v>
+        <v>78.37875</v>
       </c>
       <c r="C5" t="n">
-        <v>78.24357142857141</v>
+        <v>78.2375</v>
       </c>
       <c r="D5" t="n">
-        <v>115.0254242703645</v>
+        <v>114.2754433615594</v>
       </c>
       <c r="E5" t="n">
-        <v>111.1912434613524</v>
+        <v>109.8817702508388</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5365384615384615</v>
+        <v>0.5340086830680174</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1472066637943415</v>
+        <v>0.1500809739208131</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3025291828793774</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3115384615384615</v>
+        <v>0.3121080559575494</v>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>12.53125</v>
       </c>
       <c r="K5" t="n">
-        <v>10.89285714285714</v>
+        <v>10.96875</v>
       </c>
       <c r="L5" t="n">
-        <v>6.357142857142857</v>
+        <v>6.09375</v>
       </c>
       <c r="M5" t="n">
-        <v>12.25</v>
+        <v>12.46875</v>
       </c>
       <c r="N5" t="n">
-        <v>29.21428571428572</v>
+        <v>29.25</v>
       </c>
       <c r="O5" t="n">
-        <v>37.32142857142857</v>
+        <v>37.4375</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5741758241758241</v>
+        <v>0.5779064158224795</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.071428571428571</v>
+        <v>6.03125</v>
       </c>
       <c r="R5" t="n">
-        <v>13.39285714285714</v>
+        <v>13.3125</v>
       </c>
       <c r="S5" t="n">
-        <v>0.206043956043956</v>
+        <v>0.2054992764109985</v>
       </c>
       <c r="T5" t="n">
-        <v>2.964285714285714</v>
+        <v>2.84375</v>
       </c>
       <c r="U5" t="n">
-        <v>8.392857142857142</v>
+        <v>8.09375</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1291208791208791</v>
+        <v>0.1249397009165461</v>
       </c>
       <c r="W5" t="n">
-        <v>2.928571428571428</v>
+        <v>3.09375</v>
       </c>
       <c r="X5" t="n">
-        <v>8.535714285714286</v>
+        <v>8.90625</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1313186813186813</v>
+        <v>0.1374819102749638</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.321428571428571</v>
+        <v>8.03125</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.14285714285714</v>
+        <v>22.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3560439560439561</v>
+        <v>0.3511818620356971</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7827751196172249</v>
+        <v>0.7813021702838063</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4533333333333333</v>
+        <v>0.4530516431924883</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3531914893617021</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3430962343096234</v>
+        <v>0.3473684210526316</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3595679012345679</v>
+        <v>0.353021978021978</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.56555023923445</v>
+        <v>1.562604340567613</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.7063829787234043</v>
+        <v>0.7027027027027027</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.065388951521984</v>
+        <v>1.054294175715696</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.875</v>
+        <v>0.8717391304347826</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.9807073954983921</v>
+        <v>0.9831932773109243</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.521367521367521</v>
+        <v>1.511627906976744</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.376693766937669</v>
+        <v>1.348837209302326</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.932249322493225</v>
+        <v>4.82093023255814</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.308943089430894</v>
+        <v>6.169767441860465</v>
       </c>
     </row>
     <row r="7">
@@ -1559,7 +1559,7 @@
         <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.257</v>
+        <v>0.255</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>0.14</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="9">
@@ -1578,156 +1578,156 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="D9" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E9" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="F9" t="n">
+        <v>42</v>
+      </c>
+      <c r="G9" t="n">
+        <v>128</v>
+      </c>
+      <c r="H9" t="n">
+        <v>44</v>
+      </c>
+      <c r="I9" t="n">
+        <v>76</v>
+      </c>
+      <c r="J9" t="n">
+        <v>33</v>
+      </c>
+      <c r="K9" t="n">
+        <v>106</v>
+      </c>
+      <c r="L9" t="n">
+        <v>35</v>
+      </c>
+      <c r="M9" t="n">
+        <v>24</v>
+      </c>
+      <c r="N9" t="n">
+        <v>23</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>49</v>
+      </c>
+      <c r="R9" t="n">
+        <v>71</v>
+      </c>
+      <c r="S9" t="n">
+        <v>81</v>
+      </c>
+      <c r="T9" t="n">
+        <v>324</v>
+      </c>
+      <c r="U9" t="n">
+        <v>36</v>
+      </c>
+      <c r="V9" t="n">
         <v>41</v>
       </c>
-      <c r="G9" t="n">
-        <v>115</v>
-      </c>
-      <c r="H9" t="n">
-        <v>42</v>
-      </c>
-      <c r="I9" t="n">
-        <v>74</v>
-      </c>
-      <c r="J9" t="n">
-        <v>30</v>
-      </c>
-      <c r="K9" t="n">
-        <v>90</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="W9" t="n">
         <v>27</v>
       </c>
-      <c r="M9" t="n">
-        <v>20</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="X9" t="n">
         <v>18</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>41</v>
-      </c>
-      <c r="R9" t="n">
-        <v>59</v>
-      </c>
-      <c r="S9" t="n">
-        <v>76</v>
-      </c>
-      <c r="T9" t="n">
-        <v>313</v>
-      </c>
-      <c r="U9" t="n">
-        <v>34</v>
-      </c>
-      <c r="V9" t="n">
-        <v>39</v>
-      </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
+        <v>79</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>127</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="AB9" t="n">
         <v>24</v>
       </c>
-      <c r="X9" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>76</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>118</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.644</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>21</v>
-      </c>
       <c r="AC9" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AE9" t="n">
         <v>14</v>
       </c>
       <c r="AF9" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.424</v>
+        <v>0.4</v>
       </c>
       <c r="AH9" t="n">
         <v>8</v>
       </c>
       <c r="AI9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.381</v>
+        <v>0.32</v>
       </c>
       <c r="AK9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AL9" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.351</v>
+        <v>0.33</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>674:57</t>
+          <t>764:30</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>302.56</v>
+        <v>339.44</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.57</v>
+        <v>0.529</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.579</v>
+        <v>0.544</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.001</v>
+        <v>0.931</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.136</v>
+        <v>0.144</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.183</v>
+        <v>0.171</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.732</v>
+        <v>0.673</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.202</v>
+        <v>0.199</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.044</v>
+        <v>0.049</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.147</v>
+        <v>0.152</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.041</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="10">
@@ -1737,67 +1737,67 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>32</v>
+      </c>
+      <c r="C10" t="n">
+        <v>313</v>
+      </c>
+      <c r="D10" t="n">
+        <v>38</v>
+      </c>
+      <c r="E10" t="n">
+        <v>97</v>
+      </c>
+      <c r="F10" t="n">
+        <v>68</v>
+      </c>
+      <c r="G10" t="n">
+        <v>151</v>
+      </c>
+      <c r="H10" t="n">
+        <v>33</v>
+      </c>
+      <c r="I10" t="n">
+        <v>34</v>
+      </c>
+      <c r="J10" t="n">
+        <v>84</v>
+      </c>
+      <c r="K10" t="n">
+        <v>39</v>
+      </c>
+      <c r="L10" t="n">
         <v>28</v>
       </c>
-      <c r="C10" t="n">
-        <v>263</v>
-      </c>
-      <c r="D10" t="n">
-        <v>35</v>
-      </c>
-      <c r="E10" t="n">
-        <v>88</v>
-      </c>
-      <c r="F10" t="n">
-        <v>54</v>
-      </c>
-      <c r="G10" t="n">
-        <v>124</v>
-      </c>
-      <c r="H10" t="n">
-        <v>31</v>
-      </c>
-      <c r="I10" t="n">
-        <v>32</v>
-      </c>
-      <c r="J10" t="n">
-        <v>74</v>
-      </c>
-      <c r="K10" t="n">
-        <v>34</v>
-      </c>
-      <c r="L10" t="n">
-        <v>19</v>
-      </c>
       <c r="M10" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="Q10" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="R10" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="S10" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="T10" t="n">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="U10" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="V10" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="W10" t="n">
         <v>12</v>
@@ -1806,13 +1806,13 @@
         <v>7</v>
       </c>
       <c r="Y10" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Z10" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.902</v>
+        <v>0.891</v>
       </c>
       <c r="AB10" t="n">
         <v>13</v>
@@ -1824,69 +1824,69 @@
         <v>0.371</v>
       </c>
       <c r="AE10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF10" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.206</v>
+        <v>0.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AI10" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.389</v>
+        <v>0.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="AL10" t="n">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.443</v>
+        <v>0.441</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>605:43</t>
+          <t>689:39</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>283.08</v>
+        <v>329.96</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.547</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.582</v>
+        <v>0.595</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.929</v>
+        <v>0.949</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.201</v>
+        <v>0.203</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.146</v>
+        <v>0.133</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.298</v>
+        <v>1.254</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.211</v>
+        <v>0.214</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.034</v>
+        <v>0.044</v>
       </c>
       <c r="AX10" t="n">
         <v>0.062</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="11">
@@ -1896,98 +1896,98 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L11" t="n">
         <v>5</v>
       </c>
       <c r="M11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+      <c r="R11" t="n">
+        <v>16</v>
+      </c>
+      <c r="S11" t="n">
+        <v>28</v>
+      </c>
+      <c r="T11" t="n">
+        <v>59</v>
+      </c>
+      <c r="U11" t="n">
+        <v>9</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
         <v>2</v>
       </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6</v>
-      </c>
-      <c r="R11" t="n">
-        <v>9</v>
-      </c>
-      <c r="S11" t="n">
-        <v>8</v>
-      </c>
-      <c r="T11" t="n">
-        <v>21</v>
-      </c>
-      <c r="U11" t="n">
-        <v>5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>2</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
@@ -2004,48 +2004,48 @@
         <v>1</v>
       </c>
       <c r="AL11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>44:19</t>
+          <t>109:57</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>23.88</v>
+        <v>65</v>
       </c>
       <c r="AP11" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>0.5590000000000001</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>0.587</v>
-      </c>
       <c r="AR11" t="n">
-        <v>0.879</v>
+        <v>0.877</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.251</v>
+        <v>0.215</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.118</v>
+        <v>0.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.167</v>
+        <v>0.571</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.243</v>
+        <v>0.265</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.124</v>
+        <v>0.049</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.149</v>
+        <v>0.09</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2195,13 +2195,13 @@
         <v>0.25</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.162</v>
+        <v>0.161</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.153</v>
+        <v>0.154</v>
       </c>
       <c r="AY12" t="n">
         <v>0.001</v>
@@ -2214,40 +2214,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E13" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="H13" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I13" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J13" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K13" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="L13" t="n">
+        <v>27</v>
+      </c>
+      <c r="M13" t="n">
         <v>21</v>
-      </c>
-      <c r="M13" t="n">
-        <v>18</v>
       </c>
       <c r="N13" t="n">
         <v>8</v>
@@ -2256,108 +2256,108 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q13" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="R13" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="S13" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="T13" t="n">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="U13" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="V13" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="W13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y13" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="Z13" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.845</v>
+        <v>0.859</v>
       </c>
       <c r="AB13" t="n">
         <v>6</v>
       </c>
       <c r="AC13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI13" t="n">
         <v>34</v>
       </c>
-      <c r="AG13" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>31</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>0.355</v>
+        <v>0.353</v>
       </c>
       <c r="AK13" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AL13" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.422</v>
+        <v>0.398</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>544:27</t>
+          <t>624:20</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>233.2</v>
+        <v>267.96</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.555</v>
+        <v>0.543</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.609</v>
+        <v>0.597</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.076</v>
+        <v>1.037</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.116</v>
+        <v>0.131</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.269</v>
+        <v>0.256</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.444</v>
+        <v>1.257</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.193</v>
+        <v>0.192</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.042</v>
+        <v>0.046</v>
       </c>
       <c r="AX13" t="n">
         <v>0.109</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C14" t="n">
         <v>43</v>
@@ -2382,13 +2382,13 @@
         <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" t="n">
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H14" t="n">
         <v>11</v>
@@ -2397,7 +2397,7 @@
         <v>14</v>
       </c>
       <c r="J14" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K14" t="n">
         <v>6</v>
@@ -2406,7 +2406,7 @@
         <v>6</v>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
@@ -2415,19 +2415,19 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S14" t="n">
         <v>18</v>
       </c>
       <c r="T14" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="U14" t="n">
         <v>2</v>
@@ -2463,10 +2463,10 @@
         <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AH14" t="n">
         <v>1</v>
@@ -2481,48 +2481,48 @@
         <v>7</v>
       </c>
       <c r="AL14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AM14" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>172:50</t>
+        </is>
+      </c>
+      <c r="AO14" t="n">
+        <v>71.16</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AT14" t="n">
         <v>0.25</v>
       </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>155:12</t>
-        </is>
-      </c>
-      <c r="AO14" t="n">
-        <v>66.16</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0.456</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0.287</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0.268</v>
-      </c>
       <c r="AU14" t="n">
-        <v>1.632</v>
+        <v>1.619</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.193</v>
+        <v>0.184</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.042</v>
+        <v>0.037</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.042</v>
+        <v>0.038</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.037</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="15">
@@ -2532,22 +2532,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C15" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E15" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="H15" t="n">
         <v>31</v>
@@ -2556,16 +2556,16 @@
         <v>35</v>
       </c>
       <c r="J15" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K15" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N15" t="n">
         <v>6</v>
@@ -2574,19 +2574,19 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q15" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="R15" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="S15" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T15" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="U15" t="n">
         <v>13</v>
@@ -2595,10 +2595,10 @@
         <v>18</v>
       </c>
       <c r="W15" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15" t="n">
         <v>37</v>
@@ -2610,78 +2610,78 @@
         <v>0.881</v>
       </c>
       <c r="AB15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC15" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.385</v>
+        <v>0.367</v>
       </c>
       <c r="AE15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.5</v>
+        <v>0.417</v>
       </c>
       <c r="AK15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL15" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.262</v>
+        <v>0.252</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>402:41</t>
+          <t>441:48</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>197.4</v>
+        <v>217.4</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.412</v>
+        <v>0.401</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.464</v>
+        <v>0.449</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.821</v>
+        <v>0.791</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.117</v>
+        <v>0.12</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.195</v>
+        <v>0.176</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.696</v>
+        <v>2.538</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.221</v>
+        <v>0.22</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.104</v>
+        <v>0.115</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.078</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="16">
@@ -2691,156 +2691,156 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C16" t="n">
-        <v>359</v>
+        <v>425</v>
       </c>
       <c r="D16" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="E16" t="n">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F16" t="n">
+        <v>71</v>
+      </c>
+      <c r="G16" t="n">
+        <v>192</v>
+      </c>
+      <c r="H16" t="n">
+        <v>68</v>
+      </c>
+      <c r="I16" t="n">
+        <v>84</v>
+      </c>
+      <c r="J16" t="n">
+        <v>165</v>
+      </c>
+      <c r="K16" t="n">
+        <v>56</v>
+      </c>
+      <c r="L16" t="n">
+        <v>19</v>
+      </c>
+      <c r="M16" t="n">
+        <v>26</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>75</v>
+      </c>
+      <c r="R16" t="n">
+        <v>54</v>
+      </c>
+      <c r="S16" t="n">
+        <v>107</v>
+      </c>
+      <c r="T16" t="n">
+        <v>446</v>
+      </c>
+      <c r="U16" t="n">
+        <v>56</v>
+      </c>
+      <c r="V16" t="n">
+        <v>51</v>
+      </c>
+      <c r="W16" t="n">
+        <v>14</v>
+      </c>
+      <c r="X16" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>87</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>117</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>47</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>84</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="AK16" t="n">
         <v>61</v>
       </c>
-      <c r="G16" t="n">
-        <v>166</v>
-      </c>
-      <c r="H16" t="n">
-        <v>60</v>
-      </c>
-      <c r="I16" t="n">
-        <v>74</v>
-      </c>
-      <c r="J16" t="n">
-        <v>144</v>
-      </c>
-      <c r="K16" t="n">
-        <v>51</v>
-      </c>
-      <c r="L16" t="n">
-        <v>16</v>
-      </c>
-      <c r="M16" t="n">
-        <v>23</v>
-      </c>
-      <c r="N16" t="n">
-        <v>5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>61</v>
-      </c>
-      <c r="R16" t="n">
-        <v>49</v>
-      </c>
-      <c r="S16" t="n">
-        <v>89</v>
-      </c>
-      <c r="T16" t="n">
-        <v>380</v>
-      </c>
-      <c r="U16" t="n">
-        <v>50</v>
-      </c>
-      <c r="V16" t="n">
-        <v>30</v>
-      </c>
-      <c r="W16" t="n">
-        <v>9</v>
-      </c>
-      <c r="X16" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>72</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>97</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>77</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>52</v>
-      </c>
       <c r="AL16" t="n">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.344</v>
+        <v>0.351</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>719:09</t>
+          <t>822:36</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>395.56</v>
+        <v>467.96</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.495</v>
+        <v>0.501</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.537</v>
+        <v>0.541</v>
       </c>
       <c r="AR16" t="n">
         <v>0.908</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.154</v>
+        <v>0.16</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.199</v>
+        <v>0.191</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.361</v>
+        <v>2.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.248</v>
+        <v>0.255</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.078</v>
+        <v>0.075</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.199</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="17">
@@ -2850,67 +2850,67 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C17" t="n">
-        <v>307</v>
+        <v>346</v>
       </c>
       <c r="D17" t="n">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="E17" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="F17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H17" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="I17" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="J17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K17" t="n">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="L17" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="M17" t="n">
         <v>20</v>
       </c>
       <c r="N17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q17" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="R17" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="S17" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="T17" t="n">
-        <v>392</v>
+        <v>451</v>
       </c>
       <c r="U17" t="n">
         <v>27</v>
       </c>
       <c r="V17" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="W17" t="n">
         <v>21</v>
@@ -2919,87 +2919,87 @@
         <v>12</v>
       </c>
       <c r="Y17" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="Z17" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.831</v>
+        <v>0.833</v>
       </c>
       <c r="AB17" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AC17" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.533</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
       </c>
       <c r="AF17" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.531</v>
+        <v>0.515</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.396</v>
+        <v>0.385</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>597:20</t>
+          <t>683:20</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>261.4</v>
+        <v>292.8</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.653</v>
+        <v>0.655</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.696</v>
+        <v>0.698</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.174</v>
+        <v>1.182</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.157</v>
+        <v>0.154</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.372</v>
+        <v>0.369</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.878</v>
+        <v>0.822</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.198</v>
+        <v>0.192</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.099</v>
+        <v>0.102</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.195</v>
+        <v>0.196</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.049</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="18">
@@ -3009,67 +3009,67 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>36</v>
+      </c>
+      <c r="D18" t="n">
+        <v>13</v>
+      </c>
+      <c r="E18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" t="n">
+        <v>14</v>
+      </c>
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="C18" t="n">
+      <c r="K18" t="n">
         <v>13</v>
       </c>
-      <c r="D18" t="n">
+      <c r="L18" t="n">
         <v>5</v>
       </c>
-      <c r="E18" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>15</v>
+      </c>
+      <c r="S18" t="n">
+        <v>13</v>
+      </c>
+      <c r="T18" t="n">
+        <v>35</v>
+      </c>
+      <c r="U18" t="n">
         <v>2</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>13</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W18" t="n">
         <v>2</v>
@@ -3078,87 +3078,87 @@
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="Z18" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="AA18" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
         <v>4</v>
       </c>
-      <c r="AD18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
       <c r="AM18" t="n">
         <v>0</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>68:52</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>10.32</v>
+        <v>36.16</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.714</v>
+        <v>0.542</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.781</v>
+        <v>0.597</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.26</v>
+        <v>0.996</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.194</v>
+        <v>0.166</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.429</v>
+        <v>0.417</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.286</v>
+        <v>0.235</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.202</v>
+        <v>0.208</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="19">
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.214</v>
+        <v>0.215</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" t="n">
         <v>8</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.115</v>
+        <v>0.114</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.095</v>
+        <v>0.093</v>
       </c>
       <c r="AX21" t="n">
         <v>0.024</v>
@@ -3785,16 +3785,16 @@
         <v>1.048</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.177</v>
+        <v>0.175</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
       <c r="AX22" t="n">
         <v>0.188</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.028</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="23">
@@ -3804,22 +3804,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C23" t="n">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="D23" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E23" t="n">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="F23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G23" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="H23" t="n">
         <v>39</v>
@@ -3828,132 +3828,132 @@
         <v>57</v>
       </c>
       <c r="J23" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K23" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="L23" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M23" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N23" t="n">
+        <v>14</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>24</v>
+      </c>
+      <c r="R23" t="n">
+        <v>65</v>
+      </c>
+      <c r="S23" t="n">
+        <v>48</v>
+      </c>
+      <c r="T23" t="n">
+        <v>279</v>
+      </c>
+      <c r="U23" t="n">
+        <v>24</v>
+      </c>
+      <c r="V23" t="n">
+        <v>28</v>
+      </c>
+      <c r="W23" t="n">
+        <v>27</v>
+      </c>
+      <c r="X23" t="n">
         <v>13</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>17</v>
-      </c>
-      <c r="R23" t="n">
-        <v>57</v>
-      </c>
-      <c r="S23" t="n">
-        <v>44</v>
-      </c>
-      <c r="T23" t="n">
-        <v>257</v>
-      </c>
-      <c r="U23" t="n">
-        <v>21</v>
-      </c>
-      <c r="V23" t="n">
-        <v>24</v>
-      </c>
-      <c r="W23" t="n">
-        <v>25</v>
-      </c>
-      <c r="X23" t="n">
-        <v>12</v>
-      </c>
       <c r="Y23" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="Z23" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.705</v>
+        <v>0.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AC23" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.421</v>
+        <v>0.422</v>
       </c>
       <c r="AE23" t="n">
         <v>7</v>
       </c>
       <c r="AF23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.583</v>
+        <v>0.538</v>
       </c>
       <c r="AH23" t="n">
         <v>7</v>
       </c>
       <c r="AI23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.318</v>
+        <v>0.304</v>
       </c>
       <c r="AK23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL23" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.286</v>
+        <v>0.293</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>665:20</t>
+          <t>764:12</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>187.08</v>
+        <v>214.08</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.528</v>
+        <v>0.518</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.552</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.026</v>
+        <v>0.981</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.091</v>
+        <v>0.112</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.269</v>
+        <v>0.236</v>
       </c>
       <c r="AU23" t="n">
-        <v>2</v>
+        <v>1.583</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.127</v>
+        <v>0.125</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.063</v>
+        <v>0.066</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.147</v>
+        <v>0.142</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="24">
@@ -3963,16 +3963,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C24" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="D24" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E24" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3981,22 +3981,22 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I24" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K24" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L24" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N24" t="n">
         <v>17</v>
@@ -4005,58 +4005,58 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q24" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R24" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="S24" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="T24" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="U24" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V24" t="n">
         <v>36</v>
       </c>
       <c r="W24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="X24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y24" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="Z24" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.658</v>
+        <v>0.644</v>
       </c>
       <c r="AB24" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AC24" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.588</v>
+        <v>0.585</v>
       </c>
       <c r="AE24" t="n">
         <v>8</v>
       </c>
       <c r="AF24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.421</v>
+        <v>0.4</v>
       </c>
       <c r="AH24" t="n">
         <v>0</v>
@@ -4078,38 +4078,38 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>330:06</t>
+          <t>351:41</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>180.48</v>
+        <v>193</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.634</v>
+        <v>0.615</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.639</v>
+        <v>0.626</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.08</v>
+        <v>1.057</v>
       </c>
       <c r="AS24" t="n">
         <v>0.155</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.317</v>
+        <v>0.338</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.357</v>
+        <v>0.367</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.247</v>
+        <v>0.246</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.133</v>
+        <v>0.134</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.157</v>
+        <v>0.156</v>
       </c>
       <c r="AY24" t="n">
         <v>0.013</v>
@@ -4122,67 +4122,67 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C25" t="n">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="D25" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E25" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F25" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G25" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I25" t="n">
+        <v>20</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34</v>
+      </c>
+      <c r="K25" t="n">
+        <v>69</v>
+      </c>
+      <c r="L25" t="n">
+        <v>20</v>
+      </c>
+      <c r="M25" t="n">
+        <v>12</v>
+      </c>
+      <c r="N25" t="n">
+        <v>18</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>15</v>
+      </c>
+      <c r="R25" t="n">
+        <v>74</v>
+      </c>
+      <c r="S25" t="n">
         <v>17</v>
       </c>
-      <c r="J25" t="n">
-        <v>30</v>
-      </c>
-      <c r="K25" t="n">
-        <v>60</v>
-      </c>
-      <c r="L25" t="n">
-        <v>17</v>
-      </c>
-      <c r="M25" t="n">
-        <v>11</v>
-      </c>
-      <c r="N25" t="n">
-        <v>17</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>12</v>
-      </c>
-      <c r="R25" t="n">
-        <v>63</v>
-      </c>
-      <c r="S25" t="n">
-        <v>16</v>
-      </c>
       <c r="T25" t="n">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="U25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W25" t="n">
         <v>11</v>
@@ -4191,84 +4191,84 @@
         <v>6</v>
       </c>
       <c r="Y25" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Z25" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.96</v>
+        <v>0.906</v>
       </c>
       <c r="AB25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC25" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.533</v>
+        <v>0.556</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
       </c>
       <c r="AF25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.435</v>
+        <v>0.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI25" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.306</v>
+        <v>0.342</v>
       </c>
       <c r="AK25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL25" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.286</v>
+        <v>0.281</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>474:29</t>
+          <t>537:17</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>150.48</v>
+        <v>173.8</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.485</v>
+        <v>0.497</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.516</v>
+        <v>0.526</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.95</v>
+        <v>0.961</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.08</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.122</v>
+        <v>0.12</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.5</v>
+        <v>2.267</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.143</v>
+        <v>0.145</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.139</v>
+        <v>0.141</v>
       </c>
       <c r="AY25" t="n">
         <v>0.038</v>
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -4308,10 +4308,10 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L26" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -4323,13 +4323,13 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -4436,157 +4436,157 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2751</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>603</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1105</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1028</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>498</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>657</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>581</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>681</v>
       </c>
       <c r="T27" t="n">
-        <v>67</v>
+        <v>2976</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>785</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>408</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>0.475</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>0.371</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>831</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>0.332</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>6450:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>19</v>
+        <v>2882.08</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>0.528</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>0.955</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>0.233</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.263</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -4595,148 +4595,148 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C28" t="n">
-        <v>2436</v>
+        <v>2861</v>
       </c>
       <c r="D28" t="n">
-        <v>532</v>
+        <v>573</v>
       </c>
       <c r="E28" t="n">
-        <v>962</v>
+        <v>1060</v>
       </c>
       <c r="F28" t="n">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="G28" t="n">
-        <v>899</v>
+        <v>1013</v>
       </c>
       <c r="H28" t="n">
-        <v>442</v>
+        <v>647</v>
       </c>
       <c r="I28" t="n">
-        <v>584</v>
+        <v>823</v>
       </c>
       <c r="J28" t="n">
-        <v>517</v>
+        <v>580</v>
       </c>
       <c r="K28" t="n">
-        <v>717</v>
+        <v>818</v>
       </c>
       <c r="L28" t="n">
-        <v>316</v>
+        <v>357</v>
       </c>
       <c r="M28" t="n">
-        <v>167</v>
+        <v>247</v>
       </c>
       <c r="N28" t="n">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>384</v>
+        <v>430</v>
       </c>
       <c r="Q28" t="n">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="R28" t="n">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="S28" t="n">
-        <v>595</v>
+        <v>768</v>
       </c>
       <c r="T28" t="n">
-        <v>2656</v>
+        <v>3335</v>
       </c>
       <c r="U28" t="n">
-        <v>292</v>
+        <v>401</v>
       </c>
       <c r="V28" t="n">
-        <v>293</v>
+        <v>351</v>
       </c>
       <c r="W28" t="n">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="X28" t="n">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="Y28" t="n">
-        <v>688</v>
+        <v>936</v>
       </c>
       <c r="Z28" t="n">
-        <v>899</v>
+        <v>1198</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.765</v>
+        <v>0.781</v>
       </c>
       <c r="AB28" t="n">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="AC28" t="n">
-        <v>353</v>
+        <v>426</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.482</v>
+        <v>0.453</v>
       </c>
       <c r="AE28" t="n">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="AF28" t="n">
-        <v>294</v>
+        <v>259</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.395</v>
+        <v>0.351</v>
       </c>
       <c r="AH28" t="n">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="AI28" t="n">
-        <v>171</v>
+        <v>285</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.368</v>
+        <v>0.347</v>
       </c>
       <c r="AK28" t="n">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="AL28" t="n">
         <v>728</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.339</v>
+        <v>0.353</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>5650:00</t>
+          <t>6450:00</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>2501.96</v>
+        <v>2865.12</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.536</v>
+        <v>0.534</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.575</v>
+        <v>0.587</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.974</v>
+        <v>0.999</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.153</v>
+        <v>0.15</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.238</v>
+        <v>0.312</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.346</v>
+        <v>1.349</v>
       </c>
       <c r="AV28" t="n">
         <v>0.2</v>
@@ -4745,7 +4745,7 @@
         <v>0.061</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.139</v>
+        <v>0.136</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -4754,789 +4754,789 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>28</v>
-      </c>
-      <c r="C29" t="n">
-        <v>2520</v>
-      </c>
-      <c r="D29" t="n">
-        <v>504</v>
-      </c>
-      <c r="E29" t="n">
-        <v>933</v>
-      </c>
-      <c r="F29" t="n">
-        <v>315</v>
-      </c>
-      <c r="G29" t="n">
-        <v>887</v>
-      </c>
-      <c r="H29" t="n">
-        <v>567</v>
-      </c>
-      <c r="I29" t="n">
-        <v>722</v>
-      </c>
-      <c r="J29" t="n">
-        <v>508</v>
-      </c>
-      <c r="K29" t="n">
-        <v>716</v>
-      </c>
-      <c r="L29" t="n">
-        <v>311</v>
-      </c>
-      <c r="M29" t="n">
-        <v>205</v>
-      </c>
-      <c r="N29" t="n">
-        <v>130</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>369</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>343</v>
-      </c>
-      <c r="R29" t="n">
-        <v>605</v>
-      </c>
-      <c r="S29" t="n">
-        <v>665</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2925</v>
-      </c>
-      <c r="U29" t="n">
-        <v>336</v>
-      </c>
-      <c r="V29" t="n">
-        <v>305</v>
-      </c>
-      <c r="W29" t="n">
-        <v>178</v>
-      </c>
-      <c r="X29" t="n">
-        <v>117</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>818</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1045</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>170</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>375</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0.453</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>83</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>235</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>82</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>239</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>233</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>648</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>5650:00</t>
-        </is>
-      </c>
-      <c r="AO29" t="n">
-        <v>2506.68</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0.537</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0.589</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>1.377</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="inlineStr"/>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AU30" t="inlineStr"/>
-      <c r="AV30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr"/>
-      <c r="AX30" t="inlineStr"/>
-      <c r="AY30" t="inlineStr"/>
+          <t>#2 M. FJELLERUP (Per Game)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="T30" t="n">
+        <v>18</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>5.333</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AO30" t="n">
+        <v>7.467</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0.036</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#2 M. FJELLERUP (Per Game)</t>
+          <t>#4 P. BUSQUETS (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>6.667</v>
+        <v>9.875</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>2.281</v>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>4.031</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1.312</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>2.667</v>
+        <v>1.375</v>
       </c>
       <c r="I31" t="n">
-        <v>3.333</v>
+        <v>2.375</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>1.031</v>
       </c>
       <c r="K31" t="n">
-        <v>1.667</v>
+        <v>3.312</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.094</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0.719</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>1.531</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>1.531</v>
       </c>
       <c r="R31" t="n">
-        <v>2.333</v>
+        <v>2.219</v>
       </c>
       <c r="S31" t="n">
-        <v>2.667</v>
+        <v>2.531</v>
       </c>
       <c r="T31" t="n">
-        <v>18</v>
+        <v>324</v>
       </c>
       <c r="U31" t="n">
-        <v>1.667</v>
+        <v>1.125</v>
       </c>
       <c r="V31" t="n">
-        <v>0.667</v>
+        <v>1.281</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>0.844</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="Y31" t="n">
-        <v>4</v>
+        <v>2.469</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.333</v>
+        <v>3.969</v>
       </c>
       <c r="AA31" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="AB31" t="n">
         <v>0.75</v>
       </c>
-      <c r="AB31" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AC31" t="n">
-        <v>1.333</v>
+        <v>1.344</v>
       </c>
       <c r="AD31" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH31" t="n">
         <v>0.25</v>
       </c>
-      <c r="AE31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>0.781</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.062</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>3.219</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>7.467</v>
+        <v>10.607</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.4</v>
+        <v>0.529</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.515</v>
+        <v>0.544</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.893</v>
+        <v>0.931</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.134</v>
+        <v>0.144</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.533</v>
+        <v>0.171</v>
       </c>
       <c r="AU31" t="n">
-        <v>1</v>
+        <v>0.673</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.257</v>
+        <v>0.199</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.14</v>
+        <v>0.152</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.036</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#4 P. BUSQUETS (Per Game)</t>
+          <t>#5 D. NEEDHAM (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>10.821</v>
+        <v>9.781000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>2.464</v>
+        <v>1.188</v>
       </c>
       <c r="E32" t="n">
-        <v>4.071</v>
+        <v>3.031</v>
       </c>
       <c r="F32" t="n">
-        <v>1.464</v>
+        <v>2.125</v>
       </c>
       <c r="G32" t="n">
-        <v>4.107</v>
+        <v>4.719</v>
       </c>
       <c r="H32" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.094</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.094</v>
+      </c>
+      <c r="R32" t="n">
+        <v>3.188</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.031</v>
+      </c>
+      <c r="T32" t="n">
+        <v>258</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.5</v>
       </c>
-      <c r="I32" t="n">
-        <v>2.643</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1.071</v>
-      </c>
-      <c r="K32" t="n">
-        <v>3.214</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.964</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.464</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1.464</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2.107</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.714</v>
-      </c>
-      <c r="T32" t="n">
-        <v>313</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.214</v>
-      </c>
       <c r="V32" t="n">
-        <v>1.393</v>
+        <v>1.438</v>
       </c>
       <c r="W32" t="n">
-        <v>0.857</v>
+        <v>0.375</v>
       </c>
       <c r="X32" t="n">
-        <v>0.607</v>
+        <v>0.219</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.714</v>
+        <v>1.531</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.214</v>
+        <v>1.719</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.644</v>
+        <v>0.891</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.75</v>
+        <v>0.406</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.321</v>
+        <v>1.094</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.371</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.5</v>
+        <v>0.281</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.179</v>
+        <v>1.281</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.424</v>
+        <v>0.22</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.286</v>
+        <v>0.375</v>
       </c>
       <c r="AI32" t="n">
         <v>0.75</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.381</v>
+        <v>0.5</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.179</v>
+        <v>1.75</v>
       </c>
       <c r="AL32" t="n">
-        <v>3.357</v>
+        <v>3.969</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.351</v>
+        <v>0.441</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>24:06</t>
+          <t>21:33</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>10.806</v>
+        <v>10.311</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.57</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.579</v>
+        <v>0.595</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.001</v>
+        <v>0.949</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.136</v>
+        <v>0.203</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.183</v>
+        <v>0.133</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.732</v>
+        <v>1.254</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.202</v>
+        <v>0.214</v>
       </c>
       <c r="AW32" t="n">
         <v>0.044</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.147</v>
+        <v>0.062</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.041</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#5 D. NEEDHAM (Per Game)</t>
+          <t>#6 C. HILDRETH (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C33" t="n">
-        <v>9.393000000000001</v>
+        <v>7.125</v>
       </c>
       <c r="D33" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G33" t="n">
         <v>1.25</v>
       </c>
-      <c r="E33" t="n">
-        <v>3.143</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1.929</v>
-      </c>
-      <c r="G33" t="n">
-        <v>4.429</v>
-      </c>
       <c r="H33" t="n">
-        <v>1.107</v>
+        <v>2.5</v>
       </c>
       <c r="I33" t="n">
-        <v>1.143</v>
+        <v>3.125</v>
       </c>
       <c r="J33" t="n">
-        <v>2.643</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>1.214</v>
+        <v>1.125</v>
       </c>
       <c r="L33" t="n">
-        <v>0.679</v>
+        <v>0.625</v>
       </c>
       <c r="M33" t="n">
-        <v>0.857</v>
+        <v>0.625</v>
       </c>
       <c r="N33" t="n">
-        <v>0.321</v>
+        <v>0.5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.036</v>
+        <v>1.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.036</v>
+        <v>1.75</v>
       </c>
       <c r="R33" t="n">
-        <v>3.179</v>
+        <v>2</v>
       </c>
       <c r="S33" t="n">
-        <v>2.179</v>
+        <v>3.5</v>
       </c>
       <c r="T33" t="n">
-        <v>214</v>
+        <v>59</v>
       </c>
       <c r="U33" t="n">
-        <v>1.607</v>
+        <v>1.125</v>
       </c>
       <c r="V33" t="n">
-        <v>1.214</v>
+        <v>0.5</v>
       </c>
       <c r="W33" t="n">
-        <v>0.429</v>
+        <v>0.125</v>
       </c>
       <c r="X33" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>4.625</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
         <v>0.25</v>
       </c>
-      <c r="Y33" t="n">
-        <v>1.643</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.821</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0.902</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.371</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.214</v>
-      </c>
       <c r="AG33" t="n">
-        <v>0.206</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.643</v>
+        <v>0.5</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.389</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.679</v>
+        <v>0.125</v>
       </c>
       <c r="AL33" t="n">
-        <v>3.786</v>
+        <v>0.75</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.443</v>
+        <v>0.167</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>21:37</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>10.11</v>
+        <v>8.125</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.547</v>
+        <v>0.462</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.582</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.929</v>
+        <v>0.877</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.201</v>
+        <v>0.215</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.146</v>
+        <v>0.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.298</v>
+        <v>0.571</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.211</v>
+        <v>0.265</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.034</v>
+        <v>0.049</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.062</v>
+        <v>0.09</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.098</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#6 C. HILDRETH (Per Game)</t>
+          <t>#7 S. HOLLANDERS (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C34" t="n">
-        <v>5.25</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>0.158</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>0.211</v>
       </c>
       <c r="F34" t="n">
-        <v>0.25</v>
+        <v>0.105</v>
       </c>
       <c r="G34" t="n">
-        <v>1.25</v>
+        <v>0.368</v>
       </c>
       <c r="H34" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AD34" t="n">
         <v>0.5</v>
       </c>
-      <c r="I34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>21</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.625</v>
-      </c>
       <c r="AE34" t="n">
         <v>0</v>
       </c>
@@ -5550,1030 +5550,1030 @@
         <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.5</v>
+        <v>0.053</v>
       </c>
       <c r="AJ34" t="n">
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.25</v>
+        <v>0.105</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.75</v>
+        <v>0.316</v>
       </c>
       <c r="AM34" t="n">
         <v>0.333</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>02:15</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>5.97</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.545</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.587</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.879</v>
+        <v>0.842</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.251</v>
+        <v>0.259</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.118</v>
+        <v>0.091</v>
       </c>
       <c r="AU34" t="n">
-        <v>0.167</v>
+        <v>0.25</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.243</v>
+        <v>0.161</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.124</v>
+        <v>0.05</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.149</v>
+        <v>0.154</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#7 S. HOLLANDERS (Per Game)</t>
+          <t>#8 M. HUGHES (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6840000000000001</v>
+        <v>8.688000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>0.158</v>
+        <v>1.125</v>
       </c>
       <c r="E35" t="n">
-        <v>0.211</v>
+        <v>2.344</v>
       </c>
       <c r="F35" t="n">
-        <v>0.105</v>
+        <v>1.594</v>
       </c>
       <c r="G35" t="n">
-        <v>0.368</v>
+        <v>4.125</v>
       </c>
       <c r="H35" t="n">
-        <v>0.053</v>
+        <v>1.656</v>
       </c>
       <c r="I35" t="n">
-        <v>0.053</v>
+        <v>1.844</v>
       </c>
       <c r="J35" t="n">
-        <v>0.053</v>
+        <v>1.375</v>
       </c>
       <c r="K35" t="n">
-        <v>0.316</v>
+        <v>1.938</v>
       </c>
       <c r="L35" t="n">
-        <v>0.105</v>
+        <v>0.844</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>0.656</v>
       </c>
       <c r="N35" t="n">
-        <v>0.053</v>
+        <v>0.25</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.211</v>
+        <v>1.094</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.211</v>
+        <v>1.094</v>
       </c>
       <c r="R35" t="n">
-        <v>0.526</v>
+        <v>2.156</v>
       </c>
       <c r="S35" t="n">
-        <v>0.105</v>
+        <v>1.438</v>
       </c>
       <c r="T35" t="n">
-        <v>5</v>
+        <v>256</v>
       </c>
       <c r="U35" t="n">
-        <v>0.105</v>
+        <v>1.125</v>
       </c>
       <c r="V35" t="n">
-        <v>0.158</v>
+        <v>0.531</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>0.719</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.469</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.158</v>
+        <v>2.094</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.158</v>
+        <v>2.438</v>
       </c>
       <c r="AA35" t="n">
-        <v>1</v>
+        <v>0.859</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.053</v>
+        <v>0.188</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.105</v>
+        <v>0.625</v>
       </c>
       <c r="AD35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AE35" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.125</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.053</v>
+        <v>1.062</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>0.353</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.105</v>
+        <v>1.219</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.316</v>
+        <v>3.062</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.333</v>
+        <v>0.398</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>02:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>0.8129999999999999</v>
+        <v>8.374000000000001</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.545</v>
+        <v>0.543</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.597</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.842</v>
+        <v>1.037</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.259</v>
+        <v>0.131</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.091</v>
+        <v>0.256</v>
       </c>
       <c r="AU35" t="n">
-        <v>0.25</v>
+        <v>1.257</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.162</v>
+        <v>0.192</v>
       </c>
       <c r="AW35" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="AY35" t="n">
         <v>0.051</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>0.002</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#8 M. HUGHES (Per Game)</t>
+          <t>#9 G. FERRANDO (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C36" t="n">
-        <v>8.964</v>
+        <v>1.344</v>
       </c>
       <c r="D36" t="n">
-        <v>1.143</v>
+        <v>0.125</v>
       </c>
       <c r="E36" t="n">
-        <v>2.429</v>
+        <v>0.281</v>
       </c>
       <c r="F36" t="n">
-        <v>1.643</v>
+        <v>0.25</v>
       </c>
       <c r="G36" t="n">
-        <v>4.071</v>
+        <v>1.094</v>
       </c>
       <c r="H36" t="n">
-        <v>1.75</v>
+        <v>0.344</v>
       </c>
       <c r="I36" t="n">
-        <v>1.964</v>
+        <v>0.438</v>
       </c>
       <c r="J36" t="n">
-        <v>1.393</v>
+        <v>1.062</v>
       </c>
       <c r="K36" t="n">
-        <v>1.929</v>
+        <v>0.188</v>
       </c>
       <c r="L36" t="n">
-        <v>0.75</v>
+        <v>0.188</v>
       </c>
       <c r="M36" t="n">
-        <v>0.643</v>
+        <v>0.094</v>
       </c>
       <c r="N36" t="n">
-        <v>0.286</v>
+        <v>0.031</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.964</v>
+        <v>0.656</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.964</v>
+        <v>0.656</v>
       </c>
       <c r="R36" t="n">
-        <v>2.179</v>
+        <v>0.5</v>
       </c>
       <c r="S36" t="n">
-        <v>1.464</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="T36" t="n">
-        <v>234</v>
+        <v>39</v>
       </c>
       <c r="U36" t="n">
-        <v>1.107</v>
+        <v>0.062</v>
       </c>
       <c r="V36" t="n">
-        <v>0.429</v>
+        <v>0.094</v>
       </c>
       <c r="W36" t="n">
-        <v>0.75</v>
+        <v>0.094</v>
       </c>
       <c r="X36" t="n">
-        <v>0.5</v>
+        <v>0.031</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.143</v>
+        <v>0.375</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.536</v>
+        <v>0.469</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.845</v>
+        <v>0.8</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.214</v>
+        <v>0.031</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.643</v>
+        <v>0.094</v>
       </c>
       <c r="AD36" t="n">
         <v>0.333</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.536</v>
+        <v>0.062</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.214</v>
+        <v>0.156</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.441</v>
+        <v>0.4</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.393</v>
+        <v>0.031</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.107</v>
+        <v>0.156</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.355</v>
+        <v>0.2</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.25</v>
+        <v>0.219</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.964</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.422</v>
+        <v>0.233</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>05:24</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>8.329000000000001</v>
+        <v>2.224</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.555</v>
+        <v>0.364</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.609</v>
+        <v>0.429</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.076</v>
+        <v>0.604</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.116</v>
+        <v>0.295</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.269</v>
+        <v>0.25</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.444</v>
+        <v>1.619</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.193</v>
+        <v>0.184</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.042</v>
+        <v>0.037</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.109</v>
+        <v>0.038</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.051</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#9 G. FERRANDO (Per Game)</t>
+          <t>#10 P. VILDOZA (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C37" t="n">
-        <v>1.536</v>
+        <v>5.375</v>
       </c>
       <c r="D37" t="n">
-        <v>0.143</v>
+        <v>0.656</v>
       </c>
       <c r="E37" t="n">
-        <v>0.286</v>
+        <v>1.656</v>
       </c>
       <c r="F37" t="n">
-        <v>0.286</v>
+        <v>1.031</v>
       </c>
       <c r="G37" t="n">
-        <v>1.179</v>
+        <v>3.844</v>
       </c>
       <c r="H37" t="n">
-        <v>0.393</v>
+        <v>0.969</v>
       </c>
       <c r="I37" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.062</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.438</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>170</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="W37" t="n">
         <v>0.5</v>
       </c>
-      <c r="J37" t="n">
-        <v>1.107</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.536</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="T37" t="n">
-        <v>41</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0.107</v>
-      </c>
       <c r="X37" t="n">
-        <v>0.036</v>
+        <v>0.219</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.429</v>
+        <v>1.156</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.536</v>
+        <v>1.312</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.8</v>
+        <v>0.881</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.036</v>
+        <v>0.344</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.107</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.333</v>
+        <v>0.367</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.125</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.143</v>
+        <v>0.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.036</v>
+        <v>0.156</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.179</v>
+        <v>0.375</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.2</v>
+        <v>0.417</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.25</v>
+        <v>0.875</v>
       </c>
       <c r="AL37" t="n">
-        <v>1</v>
+        <v>3.469</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.25</v>
+        <v>0.252</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>05:32</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>2.363</v>
+        <v>6.794</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.39</v>
+        <v>0.401</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.456</v>
+        <v>0.449</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.65</v>
+        <v>0.791</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.287</v>
+        <v>0.12</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.268</v>
+        <v>0.176</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.632</v>
+        <v>2.538</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.193</v>
+        <v>0.22</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.042</v>
+        <v>0.034</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.042</v>
+        <v>0.115</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.037</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#10 P. VILDOZA (Per Game)</t>
+          <t>#11 O. LIVINGSTON (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C38" t="n">
-        <v>5.786</v>
+        <v>13.281</v>
       </c>
       <c r="D38" t="n">
-        <v>0.679</v>
+        <v>2.25</v>
       </c>
       <c r="E38" t="n">
-        <v>1.714</v>
+        <v>5.125</v>
       </c>
       <c r="F38" t="n">
-        <v>1.107</v>
+        <v>2.219</v>
       </c>
       <c r="G38" t="n">
-        <v>3.964</v>
+        <v>6</v>
       </c>
       <c r="H38" t="n">
-        <v>1.107</v>
+        <v>2.125</v>
       </c>
       <c r="I38" t="n">
-        <v>1.25</v>
+        <v>2.625</v>
       </c>
       <c r="J38" t="n">
-        <v>2.214</v>
+        <v>5.156</v>
       </c>
       <c r="K38" t="n">
-        <v>1.357</v>
+        <v>1.75</v>
       </c>
       <c r="L38" t="n">
-        <v>0.464</v>
+        <v>0.594</v>
       </c>
       <c r="M38" t="n">
-        <v>0.536</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>0.214</v>
+        <v>0.188</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.821</v>
+        <v>2.344</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.821</v>
+        <v>2.344</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>1.688</v>
       </c>
       <c r="S38" t="n">
-        <v>1.107</v>
+        <v>3.344</v>
       </c>
       <c r="T38" t="n">
-        <v>163</v>
+        <v>446</v>
       </c>
       <c r="U38" t="n">
-        <v>0.464</v>
+        <v>1.75</v>
       </c>
       <c r="V38" t="n">
-        <v>0.643</v>
+        <v>1.594</v>
       </c>
       <c r="W38" t="n">
-        <v>0.464</v>
+        <v>0.438</v>
       </c>
       <c r="X38" t="n">
-        <v>0.214</v>
+        <v>0.25</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.321</v>
+        <v>2.719</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.5</v>
+        <v>3.656</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.881</v>
+        <v>0.744</v>
       </c>
       <c r="AB38" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="AG38" t="n">
         <v>0.357</v>
       </c>
-      <c r="AC38" t="n">
-        <v>0.929</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.536</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.2</v>
-      </c>
       <c r="AH38" t="n">
-        <v>0.143</v>
+        <v>0.312</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.286</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.964</v>
+        <v>1.906</v>
       </c>
       <c r="AL38" t="n">
-        <v>3.679</v>
+        <v>5.438</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.262</v>
+        <v>0.351</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>25:42</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>7.05</v>
+        <v>14.624</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.412</v>
+        <v>0.501</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.464</v>
+        <v>0.541</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.821</v>
+        <v>0.908</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.117</v>
+        <v>0.16</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.195</v>
+        <v>0.191</v>
       </c>
       <c r="AU38" t="n">
-        <v>2.696</v>
+        <v>2.2</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.221</v>
+        <v>0.255</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.104</v>
+        <v>0.075</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.078</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#11 O. LIVINGSTON (Per Game)</t>
+          <t>#12 M. GEBEN (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C39" t="n">
-        <v>12.821</v>
+        <v>10.812</v>
       </c>
       <c r="D39" t="n">
-        <v>2.071</v>
+        <v>3.281</v>
       </c>
       <c r="E39" t="n">
-        <v>4.857</v>
+        <v>4.75</v>
       </c>
       <c r="F39" t="n">
-        <v>2.179</v>
+        <v>0.625</v>
       </c>
       <c r="G39" t="n">
-        <v>5.929</v>
+        <v>1.688</v>
       </c>
       <c r="H39" t="n">
-        <v>2.143</v>
+        <v>2.375</v>
       </c>
       <c r="I39" t="n">
-        <v>2.643</v>
+        <v>2.969</v>
       </c>
       <c r="J39" t="n">
-        <v>5.143</v>
+        <v>1.156</v>
       </c>
       <c r="K39" t="n">
-        <v>1.821</v>
+        <v>3.812</v>
       </c>
       <c r="L39" t="n">
-        <v>0.571</v>
+        <v>2.031</v>
       </c>
       <c r="M39" t="n">
-        <v>0.821</v>
+        <v>0.625</v>
       </c>
       <c r="N39" t="n">
-        <v>0.179</v>
+        <v>0.625</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.179</v>
+        <v>1.406</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.179</v>
+        <v>1.406</v>
       </c>
       <c r="R39" t="n">
-        <v>1.75</v>
+        <v>3.156</v>
       </c>
       <c r="S39" t="n">
-        <v>3.179</v>
+        <v>2.719</v>
       </c>
       <c r="T39" t="n">
-        <v>380</v>
+        <v>451</v>
       </c>
       <c r="U39" t="n">
-        <v>1.786</v>
+        <v>0.844</v>
       </c>
       <c r="V39" t="n">
-        <v>1.071</v>
+        <v>2.094</v>
       </c>
       <c r="W39" t="n">
-        <v>0.321</v>
+        <v>0.656</v>
       </c>
       <c r="X39" t="n">
-        <v>0.214</v>
+        <v>0.375</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.571</v>
+        <v>4.219</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.464</v>
+        <v>5.062</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.742</v>
+        <v>0.833</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.643</v>
+        <v>0.906</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.286</v>
+        <v>1.625</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.5</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AE39" t="n">
-        <v>1</v>
+        <v>0.531</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.75</v>
+        <v>1.031</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.364</v>
+        <v>0.515</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.321</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.536</v>
+        <v>0.062</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.857</v>
+        <v>0.625</v>
       </c>
       <c r="AL39" t="n">
-        <v>5.393</v>
+        <v>1.625</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.344</v>
+        <v>0.385</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>25:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>14.127</v>
+        <v>9.15</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.495</v>
+        <v>0.655</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.537</v>
+        <v>0.698</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.908</v>
+        <v>1.182</v>
       </c>
       <c r="AS39" t="n">
         <v>0.154</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.199</v>
+        <v>0.369</v>
       </c>
       <c r="AU39" t="n">
-        <v>2.361</v>
+        <v>0.822</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.248</v>
+        <v>0.192</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.024</v>
+        <v>0.102</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.078</v>
+        <v>0.196</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.199</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#12 M. GEBEN (Per Game)</t>
+          <t>#13 J. KARNIK (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="C40" t="n">
-        <v>10.964</v>
+        <v>7.2</v>
       </c>
       <c r="D40" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="E40" t="n">
-        <v>4.786</v>
+        <v>4</v>
       </c>
       <c r="F40" t="n">
-        <v>0.679</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>1.75</v>
+        <v>0.8</v>
       </c>
       <c r="H40" t="n">
-        <v>2.429</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>3.036</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
-        <v>1.286</v>
+        <v>0.2</v>
       </c>
       <c r="K40" t="n">
-        <v>3.786</v>
+        <v>2.6</v>
       </c>
       <c r="L40" t="n">
-        <v>1.929</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>0.714</v>
+        <v>0.4</v>
       </c>
       <c r="N40" t="n">
-        <v>0.571</v>
+        <v>0.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.464</v>
+        <v>1.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.464</v>
+        <v>1.2</v>
       </c>
       <c r="R40" t="n">
-        <v>3.214</v>
+        <v>3</v>
       </c>
       <c r="S40" t="n">
-        <v>2.643</v>
+        <v>2.6</v>
       </c>
       <c r="T40" t="n">
-        <v>392</v>
+        <v>35</v>
       </c>
       <c r="U40" t="n">
-        <v>0.964</v>
+        <v>0.4</v>
       </c>
       <c r="V40" t="n">
-        <v>2.071</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="X40" t="n">
-        <v>0.429</v>
+        <v>0.2</v>
       </c>
       <c r="Y40" t="n">
-        <v>4.214</v>
+        <v>4</v>
       </c>
       <c r="Z40" t="n">
-        <v>5.071</v>
+        <v>5</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.831</v>
+        <v>0.8</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.857</v>
+        <v>0.6</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.607</v>
+        <v>1.8</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.533</v>
+        <v>0.333</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.607</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.143</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.531</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
         <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.679</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.714</v>
+        <v>0.8</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.396</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>9.336</v>
+        <v>7.232</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.653</v>
+        <v>0.542</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.696</v>
+        <v>0.597</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.174</v>
+        <v>0.996</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.157</v>
+        <v>0.166</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.372</v>
+        <v>0.417</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.878</v>
+        <v>0.167</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.198</v>
+        <v>0.235</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.099</v>
+        <v>0.078</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.195</v>
+        <v>0.208</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.049</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#13 J. KARNIK (Per Game)</t>
+          <t>#16 I. SOLER (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -6582,16 +6582,16 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -6606,19 +6606,19 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -6627,28 +6627,28 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -6679,38 +6679,38 @@
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>10.32</v>
+        <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.714</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.781</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
         <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
         <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.202</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>
@@ -6719,11 +6719,11 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#16 I. SOLER (Per Game)</t>
+          <t>#17 E. SANMARTÍN (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -6750,13 +6750,13 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -6771,13 +6771,13 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>02:03</t>
         </is>
       </c>
       <c r="AO42" t="n">
@@ -6869,7 +6869,7 @@
         <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>0.215</v>
       </c>
       <c r="AY42" t="n">
         <v>0</v>
@@ -6878,44 +6878,44 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#17 E. SANMARTÍN (Per Game)</t>
+          <t>#20 K. BRUNOT (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.889</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0.4</v>
+        <v>0.111</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -6924,25 +6924,25 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="R43" t="n">
-        <v>0.2</v>
+        <v>0.778</v>
       </c>
       <c r="S43" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="T43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -6951,84 +6951,84 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK43" t="n">
         <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AM43" t="n">
         <v>0</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>02:03</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>0</v>
+        <v>1.307</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>0.357</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>0.457</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>0.255</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AU43" t="n">
         <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>0.114</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.214</v>
+        <v>0.024</v>
       </c>
       <c r="AY43" t="n">
         <v>0</v>
@@ -7037,316 +7037,316 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#20 K. BRUNOT (Per Game)</t>
+          <t>#21 J. FERNÁNDEZ (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>7.944</v>
       </c>
       <c r="D44" t="n">
-        <v>0.125</v>
+        <v>2.556</v>
       </c>
       <c r="E44" t="n">
-        <v>0.25</v>
+        <v>3.833</v>
       </c>
       <c r="F44" t="n">
-        <v>0.125</v>
+        <v>0.222</v>
       </c>
       <c r="G44" t="n">
-        <v>0.625</v>
+        <v>1.556</v>
       </c>
       <c r="H44" t="n">
-        <v>0.375</v>
+        <v>2.167</v>
       </c>
       <c r="I44" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3.444</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.056</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="T44" t="n">
+        <v>195</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.056</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="X44" t="n">
         <v>0.5</v>
       </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="L44" t="n">
+      <c r="Y44" t="n">
+        <v>3.778</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>4.889</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="AI44" t="n">
         <v>0.5</v>
       </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AJ44" t="n">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="AK44" t="n">
         <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.375</v>
+        <v>1.056</v>
       </c>
       <c r="AM44" t="n">
         <v>0</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>1.47</v>
+        <v>7.876</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.357</v>
+        <v>0.536</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.457</v>
+        <v>0.592</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.68</v>
+        <v>1.009</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.255</v>
+        <v>0.148</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.429</v>
+        <v>0.402</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>1.048</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.115</v>
+        <v>0.175</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.095</v>
+        <v>0.056</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.024</v>
+        <v>0.188</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#21 J. FERNÁNDEZ (Per Game)</t>
+          <t>#23 S. MARTÍNEZ (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C45" t="n">
-        <v>7.944</v>
+        <v>6.774</v>
       </c>
       <c r="D45" t="n">
-        <v>2.556</v>
+        <v>1.839</v>
       </c>
       <c r="E45" t="n">
-        <v>3.833</v>
+        <v>3.258</v>
       </c>
       <c r="F45" t="n">
-        <v>0.222</v>
+        <v>0.613</v>
       </c>
       <c r="G45" t="n">
-        <v>1.556</v>
+        <v>2.065</v>
       </c>
       <c r="H45" t="n">
-        <v>2.167</v>
+        <v>1.258</v>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>1.839</v>
       </c>
       <c r="J45" t="n">
-        <v>1.222</v>
+        <v>1.226</v>
       </c>
       <c r="K45" t="n">
-        <v>3.444</v>
+        <v>3.194</v>
       </c>
       <c r="L45" t="n">
-        <v>1.056</v>
+        <v>1.516</v>
       </c>
       <c r="M45" t="n">
-        <v>0.556</v>
+        <v>0.613</v>
       </c>
       <c r="N45" t="n">
-        <v>0.722</v>
+        <v>0.452</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.167</v>
+        <v>0.774</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.167</v>
+        <v>0.774</v>
       </c>
       <c r="R45" t="n">
-        <v>2.833</v>
+        <v>2.097</v>
       </c>
       <c r="S45" t="n">
-        <v>3.333</v>
+        <v>1.548</v>
       </c>
       <c r="T45" t="n">
-        <v>195</v>
+        <v>279</v>
       </c>
       <c r="U45" t="n">
-        <v>0.944</v>
+        <v>0.774</v>
       </c>
       <c r="V45" t="n">
-        <v>1.056</v>
+        <v>0.903</v>
       </c>
       <c r="W45" t="n">
-        <v>0.778</v>
+        <v>0.871</v>
       </c>
       <c r="X45" t="n">
-        <v>0.5</v>
+        <v>0.419</v>
       </c>
       <c r="Y45" t="n">
-        <v>3.778</v>
+        <v>2.258</v>
       </c>
       <c r="Z45" t="n">
-        <v>4.889</v>
+        <v>3.226</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.773</v>
+        <v>0.7</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.722</v>
+        <v>0.613</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.667</v>
+        <v>1.452</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.433</v>
+        <v>0.422</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.222</v>
+        <v>0.226</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.278</v>
+        <v>0.419</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.8</v>
+        <v>0.538</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.222</v>
+        <v>0.226</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.5</v>
+        <v>0.742</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.444</v>
+        <v>0.304</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.056</v>
+        <v>1.323</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>0.293</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>24:39</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>7.876</v>
+        <v>6.906</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.536</v>
+        <v>0.518</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.592</v>
+        <v>0.552</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.009</v>
+        <v>0.981</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.148</v>
+        <v>0.112</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.402</v>
+        <v>0.236</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.048</v>
+        <v>1.583</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.177</v>
+        <v>0.125</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.058</v>
+        <v>0.066</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.188</v>
+        <v>0.142</v>
       </c>
       <c r="AY45" t="n">
         <v>0.045</v>
@@ -7355,634 +7355,634 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#23 S. MARTÍNEZ (Per Game)</t>
+          <t>#25 N. MARIC (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C46" t="n">
-        <v>7.111</v>
+        <v>7.034</v>
       </c>
       <c r="D46" t="n">
-        <v>1.889</v>
+        <v>2.759</v>
       </c>
       <c r="E46" t="n">
-        <v>3.259</v>
+        <v>4.483</v>
       </c>
       <c r="F46" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>2.111</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.444</v>
+        <v>1.517</v>
       </c>
       <c r="I46" t="n">
-        <v>2.111</v>
+        <v>2.586</v>
       </c>
       <c r="J46" t="n">
-        <v>1.259</v>
+        <v>0.379</v>
       </c>
       <c r="K46" t="n">
-        <v>3.296</v>
+        <v>1.724</v>
       </c>
       <c r="L46" t="n">
-        <v>1.407</v>
+        <v>1.517</v>
       </c>
       <c r="M46" t="n">
-        <v>0.593</v>
+        <v>0.207</v>
       </c>
       <c r="N46" t="n">
-        <v>0.481</v>
+        <v>0.586</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.63</v>
+        <v>1.034</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.63</v>
+        <v>1.034</v>
       </c>
       <c r="R46" t="n">
-        <v>2.111</v>
+        <v>2.793</v>
       </c>
       <c r="S46" t="n">
-        <v>1.63</v>
+        <v>2.241</v>
       </c>
       <c r="T46" t="n">
-        <v>257</v>
+        <v>205</v>
       </c>
       <c r="U46" t="n">
-        <v>0.778</v>
+        <v>0.897</v>
       </c>
       <c r="V46" t="n">
-        <v>0.889</v>
+        <v>1.241</v>
       </c>
       <c r="W46" t="n">
-        <v>0.926</v>
+        <v>0.655</v>
       </c>
       <c r="X46" t="n">
-        <v>0.444</v>
+        <v>0.414</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.481</v>
+        <v>2.931</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.519</v>
+        <v>4.552</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.705</v>
+        <v>0.644</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.593</v>
+        <v>1.069</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.407</v>
+        <v>1.828</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.421</v>
+        <v>0.585</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.259</v>
+        <v>0.276</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.444</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.583</v>
+        <v>0.4</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.259</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.8149999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.318</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.296</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>24:38</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>6.929</v>
+        <v>6.655</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.528</v>
+        <v>0.615</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.626</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.026</v>
+        <v>1.057</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.091</v>
+        <v>0.155</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.269</v>
+        <v>0.338</v>
       </c>
       <c r="AU46" t="n">
-        <v>2</v>
+        <v>0.367</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.127</v>
+        <v>0.246</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.063</v>
+        <v>0.134</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.147</v>
+        <v>0.156</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.046</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>#25 N. MARIC (Per Game)</t>
+          <t>#29 M. SUSINSKAS (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C47" t="n">
-        <v>7.5</v>
+        <v>5.387</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.731</v>
+        <v>1.774</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>3.065</v>
       </c>
       <c r="H47" t="n">
-        <v>1.5</v>
+        <v>0.581</v>
       </c>
       <c r="I47" t="n">
-        <v>2.577</v>
+        <v>0.645</v>
       </c>
       <c r="J47" t="n">
-        <v>0.385</v>
+        <v>1.097</v>
       </c>
       <c r="K47" t="n">
-        <v>1.808</v>
+        <v>2.226</v>
       </c>
       <c r="L47" t="n">
-        <v>1.538</v>
+        <v>0.645</v>
       </c>
       <c r="M47" t="n">
-        <v>0.192</v>
+        <v>0.387</v>
       </c>
       <c r="N47" t="n">
-        <v>0.654</v>
+        <v>0.581</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.077</v>
+        <v>0.484</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.077</v>
+        <v>0.484</v>
       </c>
       <c r="R47" t="n">
-        <v>2.731</v>
+        <v>2.387</v>
       </c>
       <c r="S47" t="n">
-        <v>2.308</v>
+        <v>0.548</v>
       </c>
       <c r="T47" t="n">
-        <v>202</v>
+        <v>156</v>
       </c>
       <c r="U47" t="n">
-        <v>0.923</v>
+        <v>0.581</v>
       </c>
       <c r="V47" t="n">
-        <v>1.385</v>
+        <v>0.323</v>
       </c>
       <c r="W47" t="n">
-        <v>0.654</v>
+        <v>0.355</v>
       </c>
       <c r="X47" t="n">
-        <v>0.423</v>
+        <v>0.194</v>
       </c>
       <c r="Y47" t="n">
-        <v>3.038</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.615</v>
+        <v>1.032</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.658</v>
+        <v>0.906</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.154</v>
+        <v>0.323</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.962</v>
+        <v>0.581</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.588</v>
+        <v>0.556</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.308</v>
+        <v>0.323</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.731</v>
+        <v>0.806</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.421</v>
+        <v>0.4</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>0.419</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>1.226</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>0.342</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>0.516</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>1.839</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>0.281</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>6.942</v>
+        <v>5.606</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.634</v>
+        <v>0.497</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.639</v>
+        <v>0.526</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.08</v>
+        <v>0.961</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.155</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.317</v>
+        <v>0.12</v>
       </c>
       <c r="AU47" t="n">
-        <v>0.357</v>
+        <v>2.267</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.247</v>
+        <v>0.145</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.133</v>
+        <v>0.04</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.157</v>
+        <v>0.141</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.014</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>#29 M. SUSINSKAS (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C48" t="n">
-        <v>5.296</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.963</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1.704</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.926</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>3.148</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.593</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>1.111</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>2.222</v>
+        <v>1.969</v>
       </c>
       <c r="L48" t="n">
-        <v>0.63</v>
+        <v>1.344</v>
       </c>
       <c r="M48" t="n">
-        <v>0.407</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.444</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.444</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.333</v>
+        <v>0.219</v>
       </c>
       <c r="S48" t="n">
-        <v>0.593</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>0.593</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0.296</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>0.407</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.926</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.296</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.533</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.852</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.407</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.306</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>0.519</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.815</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>5.573</v>
+        <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.485</v>
+        <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.516</v>
+        <v>0</v>
       </c>
       <c r="AR48" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="AT48" t="n">
-        <v>0.122</v>
+        <v>0</v>
       </c>
       <c r="AU48" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.139</v>
+        <v>0</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.039</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>85.96899999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>18.844</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>34.531</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>10.906</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>32.125</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>15.562</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>20.531</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>18.156</v>
       </c>
       <c r="K49" t="n">
-        <v>2.036</v>
+        <v>25.5</v>
       </c>
       <c r="L49" t="n">
-        <v>1.25</v>
+        <v>11.969</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>6.156</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.562</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0.679</v>
+        <v>14.375</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>13.688</v>
       </c>
       <c r="R49" t="n">
-        <v>0.214</v>
+        <v>24.344</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>21.281</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2976</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>10.031</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>5.938</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>3.438</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>24.531</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>32.281</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>6.062</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>0.475</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>3.812</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>10.031</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>2.281</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>6.156</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>0.371</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>8.625</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>25.969</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>0.332</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:33</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>0</v>
+        <v>90.065</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>0.528</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>0.955</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>0.233</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>1.263</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -7991,477 +7991,159 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>89.40600000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>17.906</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>33.125</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>11.125</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>31.656</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>20.219</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>25.719</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>18.125</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>25.562</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>11.156</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>7.719</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4.594</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>13.438</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>12.469</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>21.656</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T50" t="n">
-        <v>67</v>
+        <v>3335</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>12.531</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>10.969</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>6.094</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>4.031</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>29.25</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>37.438</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>0.781</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>6.031</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>13.312</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>0.453</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>2.844</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>8.093999999999999</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>0.351</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>3.094</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>8.906000000000001</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>0.347</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>8.031000000000001</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>22.75</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>0.353</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:33</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>0.679</v>
+        <v>89.535</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>0.534</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>0.587</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>0.999</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>1.349</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>0.199</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>28</v>
-      </c>
-      <c r="C51" t="n">
-        <v>87</v>
-      </c>
-      <c r="D51" t="n">
-        <v>19</v>
-      </c>
-      <c r="E51" t="n">
-        <v>34.357</v>
-      </c>
-      <c r="F51" t="n">
-        <v>11.071</v>
-      </c>
-      <c r="G51" t="n">
-        <v>32.107</v>
-      </c>
-      <c r="H51" t="n">
-        <v>15.786</v>
-      </c>
-      <c r="I51" t="n">
-        <v>20.857</v>
-      </c>
-      <c r="J51" t="n">
-        <v>18.464</v>
-      </c>
-      <c r="K51" t="n">
-        <v>25.607</v>
-      </c>
-      <c r="L51" t="n">
-        <v>11.286</v>
-      </c>
-      <c r="M51" t="n">
-        <v>5.964</v>
-      </c>
-      <c r="N51" t="n">
-        <v>4.571</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>13.714</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>13.036</v>
-      </c>
-      <c r="R51" t="n">
-        <v>24.107</v>
-      </c>
-      <c r="S51" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2656</v>
-      </c>
-      <c r="U51" t="n">
-        <v>10.429</v>
-      </c>
-      <c r="V51" t="n">
-        <v>10.464</v>
-      </c>
-      <c r="W51" t="n">
-        <v>6.143</v>
-      </c>
-      <c r="X51" t="n">
-        <v>3.643</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>24.571</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>32.107</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>6.071</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>12.607</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>4.143</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>6.107</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>8.821</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>26</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>201:47</t>
-        </is>
-      </c>
-      <c r="AO51" t="n">
-        <v>89.35599999999999</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0.536</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>0.974</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>1.346</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>28</v>
-      </c>
-      <c r="C52" t="n">
-        <v>90</v>
-      </c>
-      <c r="D52" t="n">
-        <v>18</v>
-      </c>
-      <c r="E52" t="n">
-        <v>33.321</v>
-      </c>
-      <c r="F52" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="G52" t="n">
-        <v>31.679</v>
-      </c>
-      <c r="H52" t="n">
-        <v>20.25</v>
-      </c>
-      <c r="I52" t="n">
-        <v>25.786</v>
-      </c>
-      <c r="J52" t="n">
-        <v>18.143</v>
-      </c>
-      <c r="K52" t="n">
-        <v>25.571</v>
-      </c>
-      <c r="L52" t="n">
-        <v>11.107</v>
-      </c>
-      <c r="M52" t="n">
-        <v>7.321</v>
-      </c>
-      <c r="N52" t="n">
-        <v>4.643</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>13.179</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="R52" t="n">
-        <v>21.607</v>
-      </c>
-      <c r="S52" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2925</v>
-      </c>
-      <c r="U52" t="n">
-        <v>12</v>
-      </c>
-      <c r="V52" t="n">
-        <v>10.893</v>
-      </c>
-      <c r="W52" t="n">
-        <v>6.357</v>
-      </c>
-      <c r="X52" t="n">
-        <v>4.179</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>29.214</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>37.321</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>6.071</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>13.393</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0.453</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>2.964</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>8.393000000000001</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>2.929</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>8.536</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>8.321</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>23.143</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>201:47</t>
-        </is>
-      </c>
-      <c r="AO52" t="n">
-        <v>89.524</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>0.537</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0.589</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>1.377</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="AY52" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Bàsquet Girona.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Bàsquet Girona.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2499.08</v>
+        <v>2644.04</v>
       </c>
       <c r="C2" t="n">
-        <v>2503.6</v>
+        <v>2650.46</v>
       </c>
       <c r="D2" t="n">
-        <v>109.8817702508388</v>
+        <v>109.9054503746519</v>
       </c>
       <c r="E2" t="n">
-        <v>114.2754433615594</v>
+        <v>114.0934026546335</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5281293952180028</v>
+        <v>0.5241122314774221</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1596069505357242</v>
+        <v>0.1571547811570765</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3189009159034138</v>
+        <v>0.3268933539412674</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2334739803094233</v>
+        <v>0.2288469969311705</v>
       </c>
       <c r="J2" t="n">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="K2" t="n">
-        <v>360</v>
+        <v>393</v>
       </c>
       <c r="L2" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="M2" t="n">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="N2" t="n">
-        <v>785</v>
+        <v>827</v>
       </c>
       <c r="O2" t="n">
-        <v>1033</v>
+        <v>1089</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4842944210032817</v>
+        <v>0.4774221832529592</v>
       </c>
       <c r="Q2" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="R2" t="n">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1912798874824191</v>
+        <v>0.190267426567295</v>
       </c>
       <c r="T2" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="U2" t="n">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1504922644163151</v>
+        <v>0.154318281455502</v>
       </c>
       <c r="W2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="X2" t="n">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0923581809657759</v>
+        <v>0.0920648838228847</v>
       </c>
       <c r="Z2" t="n">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="AA2" t="n">
-        <v>831</v>
+        <v>887</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3895921237693389</v>
+        <v>0.3888645330995177</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7599225556631172</v>
+        <v>0.7594123048668503</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4754901960784313</v>
+        <v>0.4585253456221198</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3800623052959501</v>
+        <v>0.3664772727272727</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3705583756345178</v>
+        <v>0.3619047619047619</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.332129963898917</v>
+        <v>0.3370913190529876</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.519845111326234</v>
+        <v>1.518824609733701</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7601246105919003</v>
+        <v>0.7329545454545454</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.018482490272373</v>
+        <v>1.025524156791249</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7465116279069768</v>
+        <v>0.7214912280701754</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.9399477806788512</v>
+        <v>0.9290780141843972</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.727272727272727</v>
+        <v>1.736842105263158</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.263043478260869</v>
+        <v>1.265560165975104</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.636956521739131</v>
+        <v>4.732365145228216</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.9</v>
+        <v>5.99792531120332</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.09625</v>
+        <v>77.76588235294118</v>
       </c>
       <c r="C3" t="n">
-        <v>78.2375</v>
+        <v>77.95470588235294</v>
       </c>
       <c r="D3" t="n">
-        <v>109.8817702508388</v>
+        <v>109.9054503746519</v>
       </c>
       <c r="E3" t="n">
-        <v>114.2754433615594</v>
+        <v>114.0934026546335</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5281293952180028</v>
+        <v>0.524112231477422</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1596069505357242</v>
+        <v>0.1571547811570765</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3189009159034138</v>
+        <v>0.3268933539412673</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2334739803094233</v>
+        <v>0.2288469969311705</v>
       </c>
       <c r="J3" t="n">
-        <v>10.03125</v>
+        <v>9.676470588235293</v>
       </c>
       <c r="K3" t="n">
-        <v>11.25</v>
+        <v>11.55882352941176</v>
       </c>
       <c r="L3" t="n">
-        <v>5.9375</v>
+        <v>5.823529411764706</v>
       </c>
       <c r="M3" t="n">
-        <v>13.6875</v>
+        <v>13.5</v>
       </c>
       <c r="N3" t="n">
-        <v>24.53125</v>
+        <v>24.32352941176471</v>
       </c>
       <c r="O3" t="n">
-        <v>32.28125</v>
+        <v>32.02941176470588</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4842944210032817</v>
+        <v>0.4774221832529592</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.0625</v>
+        <v>5.852941176470588</v>
       </c>
       <c r="R3" t="n">
-        <v>12.75</v>
+        <v>12.76470588235294</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1912798874824191</v>
+        <v>0.190267426567295</v>
       </c>
       <c r="T3" t="n">
-        <v>3.8125</v>
+        <v>3.794117647058823</v>
       </c>
       <c r="U3" t="n">
-        <v>10.03125</v>
+        <v>10.35294117647059</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1504922644163151</v>
+        <v>0.154318281455502</v>
       </c>
       <c r="W3" t="n">
-        <v>2.28125</v>
+        <v>2.235294117647059</v>
       </c>
       <c r="X3" t="n">
-        <v>6.15625</v>
+        <v>6.176470588235294</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0923581809657759</v>
+        <v>0.09206488382288469</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.625</v>
+        <v>8.794117647058824</v>
       </c>
       <c r="AA3" t="n">
-        <v>25.96875</v>
+        <v>26.08823529411765</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3895921237693389</v>
+        <v>0.3888645330995177</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7599225556631172</v>
+        <v>0.7594123048668503</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4754901960784313</v>
+        <v>0.4585253456221198</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3800623052959501</v>
+        <v>0.3664772727272727</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3705583756345178</v>
+        <v>0.3619047619047619</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.332129963898917</v>
+        <v>0.3370913190529876</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.519845111326234</v>
+        <v>1.518824609733701</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7601246105919003</v>
+        <v>0.7329545454545454</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.018482490272373</v>
+        <v>1.025524156791249</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7465116279069768</v>
+        <v>0.7214912280701754</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9399477806788512</v>
+        <v>0.9290780141843972</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.727272727272727</v>
+        <v>1.736842105263158</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.263043478260869</v>
+        <v>1.265560165975104</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.636956521739131</v>
+        <v>4.732365145228217</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.9</v>
+        <v>5.99792531120332</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2508.12</v>
+        <v>2656.88</v>
       </c>
       <c r="C4" t="n">
-        <v>2503.6</v>
+        <v>2650.46</v>
       </c>
       <c r="D4" t="n">
-        <v>114.2754433615594</v>
+        <v>114.0934026546335</v>
       </c>
       <c r="E4" t="n">
-        <v>109.8817702508388</v>
+        <v>109.9054503746519</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5340086830680174</v>
+        <v>0.5340182648401827</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1500809739208131</v>
+        <v>0.1504017309392192</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.3024193548387097</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3121080559575494</v>
+        <v>0.3127853881278539</v>
       </c>
       <c r="J4" t="n">
-        <v>401</v>
+        <v>426</v>
       </c>
       <c r="K4" t="n">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="L4" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="M4" t="n">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="N4" t="n">
-        <v>936</v>
+        <v>992</v>
       </c>
       <c r="O4" t="n">
-        <v>1198</v>
+        <v>1271</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5779064158224795</v>
+        <v>0.580365296803653</v>
       </c>
       <c r="Q4" t="n">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="R4" t="n">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2054992764109985</v>
+        <v>0.2013698630136986</v>
       </c>
       <c r="T4" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="U4" t="n">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1249397009165461</v>
+        <v>0.1237442922374429</v>
       </c>
       <c r="W4" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="X4" t="n">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1374819102749638</v>
+        <v>0.1406392694063927</v>
       </c>
       <c r="Z4" t="n">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="AA4" t="n">
-        <v>728</v>
+        <v>776</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3511818620356971</v>
+        <v>0.354337899543379</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7813021702838063</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4530516431924883</v>
+        <v>0.4580498866213152</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3513513513513514</v>
+        <v>0.3505535055350554</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3473684210526316</v>
+        <v>0.3474025974025974</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.353021978021978</v>
+        <v>0.3479381443298969</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.562604340567613</v>
+        <v>1.560975609756098</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.7027027027027027</v>
+        <v>0.7011070110701108</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.054294175715696</v>
+        <v>1.043357933579336</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8717391304347826</v>
+        <v>0.8838174273858921</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.9831932773109243</v>
+        <v>0.968</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.511627906976744</v>
+        <v>1.533333333333333</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.348837209302326</v>
+        <v>1.346491228070176</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.82093023255814</v>
+        <v>4.802631578947368</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.169767441860465</v>
+        <v>6.149122807017544</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78.37875</v>
+        <v>78.1435294117647</v>
       </c>
       <c r="C5" t="n">
-        <v>78.2375</v>
+        <v>77.95470588235294</v>
       </c>
       <c r="D5" t="n">
-        <v>114.2754433615594</v>
+        <v>114.0934026546335</v>
       </c>
       <c r="E5" t="n">
-        <v>109.8817702508388</v>
+        <v>109.9054503746519</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5340086830680174</v>
+        <v>0.5340182648401827</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1500809739208131</v>
+        <v>0.1504017309392193</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.3024193548387097</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3121080559575494</v>
+        <v>0.3127853881278539</v>
       </c>
       <c r="J5" t="n">
-        <v>12.53125</v>
+        <v>12.52941176470588</v>
       </c>
       <c r="K5" t="n">
-        <v>10.96875</v>
+        <v>10.67647058823529</v>
       </c>
       <c r="L5" t="n">
-        <v>6.09375</v>
+        <v>6.088235294117647</v>
       </c>
       <c r="M5" t="n">
-        <v>12.46875</v>
+        <v>12.41176470588235</v>
       </c>
       <c r="N5" t="n">
-        <v>29.25</v>
+        <v>29.17647058823529</v>
       </c>
       <c r="O5" t="n">
-        <v>37.4375</v>
+        <v>37.38235294117647</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5779064158224795</v>
+        <v>0.580365296803653</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.03125</v>
+        <v>5.941176470588236</v>
       </c>
       <c r="R5" t="n">
-        <v>13.3125</v>
+        <v>12.97058823529412</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2054992764109985</v>
+        <v>0.2013698630136986</v>
       </c>
       <c r="T5" t="n">
-        <v>2.84375</v>
+        <v>2.794117647058823</v>
       </c>
       <c r="U5" t="n">
-        <v>8.09375</v>
+        <v>7.970588235294118</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1249397009165461</v>
+        <v>0.1237442922374429</v>
       </c>
       <c r="W5" t="n">
-        <v>3.09375</v>
+        <v>3.147058823529412</v>
       </c>
       <c r="X5" t="n">
-        <v>8.90625</v>
+        <v>9.058823529411764</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1374819102749638</v>
+        <v>0.1406392694063927</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.03125</v>
+        <v>7.941176470588236</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.75</v>
+        <v>22.82352941176471</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3511818620356971</v>
+        <v>0.354337899543379</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7813021702838063</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4530516431924883</v>
+        <v>0.4580498866213152</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3513513513513514</v>
+        <v>0.3505535055350553</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3473684210526316</v>
+        <v>0.3474025974025974</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.353021978021978</v>
+        <v>0.3479381443298969</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.562604340567613</v>
+        <v>1.560975609756098</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.7027027027027027</v>
+        <v>0.7011070110701106</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.054294175715696</v>
+        <v>1.043357933579336</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8717391304347826</v>
+        <v>0.8838174273858922</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.9831932773109243</v>
+        <v>0.968</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.511627906976744</v>
+        <v>1.533333333333333</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.348837209302326</v>
+        <v>1.346491228070175</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.82093023255814</v>
+        <v>4.802631578947368</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.169767441860465</v>
+        <v>6.149122807017544</v>
       </c>
     </row>
     <row r="7">
@@ -1559,7 +1559,7 @@
         <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.255</v>
+        <v>0.254</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -1578,43 +1578,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="D9" t="n">
         <v>73</v>
       </c>
       <c r="E9" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="H9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I9" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J9" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K9" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="L9" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M9" t="n">
+        <v>25</v>
+      </c>
+      <c r="N9" t="n">
         <v>24</v>
-      </c>
-      <c r="N9" t="n">
-        <v>23</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1626,16 +1626,16 @@
         <v>49</v>
       </c>
       <c r="R9" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="S9" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="T9" t="n">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="U9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V9" t="n">
         <v>41</v>
@@ -1647,22 +1647,22 @@
         <v>18</v>
       </c>
       <c r="Y9" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Z9" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.622</v>
+        <v>0.618</v>
       </c>
       <c r="AB9" t="n">
         <v>24</v>
       </c>
       <c r="AC9" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.522</v>
       </c>
       <c r="AE9" t="n">
         <v>14</v>
@@ -1677,57 +1677,57 @@
         <v>8</v>
       </c>
       <c r="AI9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.32</v>
+        <v>0.296</v>
       </c>
       <c r="AK9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AL9" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.33</v>
+        <v>0.327</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>764:30</t>
+          <t>805:36</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>339.44</v>
+        <v>350.2</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.529</v>
+        <v>0.517</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.544</v>
+        <v>0.533</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.931</v>
+        <v>0.917</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.144</v>
+        <v>0.14</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.171</v>
+        <v>0.173</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.673</v>
+        <v>0.735</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.199</v>
+        <v>0.194</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.049</v>
+        <v>0.051</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.152</v>
+        <v>0.162</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="10">
@@ -1737,82 +1737,82 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="D10" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E10" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F10" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G10" t="n">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="H10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J10" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K10" t="n">
         <v>39</v>
       </c>
       <c r="L10" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R10" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="S10" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="T10" t="n">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="U10" t="n">
         <v>48</v>
       </c>
       <c r="V10" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="W10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y10" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Z10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.891</v>
+        <v>0.9</v>
       </c>
       <c r="AB10" t="n">
         <v>13</v>
@@ -1827,66 +1827,66 @@
         <v>9</v>
       </c>
       <c r="AF10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.22</v>
+        <v>0.205</v>
       </c>
       <c r="AH10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AJ10" t="n">
         <v>0.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="AL10" t="n">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.441</v>
+        <v>0.431</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>689:39</t>
+          <t>741:51</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>329.96</v>
+        <v>357.4</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.595</v>
+        <v>0.593</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.949</v>
+        <v>0.96</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.203</v>
+        <v>0.19</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.133</v>
+        <v>0.124</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.254</v>
+        <v>1.338</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.214</v>
+        <v>0.215</v>
       </c>
       <c r="AW10" t="n">
         <v>0.044</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.062</v>
+        <v>0.058</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.099</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="11">
@@ -1896,67 +1896,67 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" t="n">
+        <v>23</v>
+      </c>
+      <c r="I11" t="n">
+        <v>28</v>
+      </c>
+      <c r="J11" t="n">
         <v>10</v>
       </c>
-      <c r="H11" t="n">
-        <v>20</v>
-      </c>
-      <c r="I11" t="n">
-        <v>25</v>
-      </c>
-      <c r="J11" t="n">
-        <v>8</v>
-      </c>
       <c r="K11" t="n">
+        <v>11</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>16</v>
+      </c>
+      <c r="R11" t="n">
+        <v>19</v>
+      </c>
+      <c r="S11" t="n">
+        <v>31</v>
+      </c>
+      <c r="T11" t="n">
+        <v>78</v>
+      </c>
+      <c r="U11" t="n">
+        <v>11</v>
+      </c>
+      <c r="V11" t="n">
         <v>9</v>
-      </c>
-      <c r="L11" t="n">
-        <v>5</v>
-      </c>
-      <c r="M11" t="n">
-        <v>5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>14</v>
-      </c>
-      <c r="R11" t="n">
-        <v>16</v>
-      </c>
-      <c r="S11" t="n">
-        <v>28</v>
-      </c>
-      <c r="T11" t="n">
-        <v>59</v>
-      </c>
-      <c r="U11" t="n">
-        <v>9</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
@@ -1965,28 +1965,28 @@
         <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Z11" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.784</v>
+        <v>0.822</v>
       </c>
       <c r="AB11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC11" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.5</v>
+        <v>0.476</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2001,51 +2001,51 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.167</v>
+        <v>0.25</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>109:57</t>
+          <t>140:22</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>65</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.462</v>
+        <v>0.491</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.572</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.877</v>
+        <v>0.924</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.215</v>
+        <v>0.192</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.5</v>
+        <v>0.418</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.571</v>
+        <v>0.625</v>
       </c>
       <c r="AV11" t="n">
         <v>0.265</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.049</v>
+        <v>0.045</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.09</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="12">
@@ -2198,7 +2198,7 @@
         <v>0.161</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="AX12" t="n">
         <v>0.154</v>
@@ -2214,64 +2214,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" t="n">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F13" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="H13" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I13" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M13" t="n">
         <v>21</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R13" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="S13" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="T13" t="n">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="U13" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="V13" t="n">
         <v>17</v>
@@ -2283,87 +2283,87 @@
         <v>15</v>
       </c>
       <c r="Y13" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="Z13" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.859</v>
+        <v>0.866</v>
       </c>
       <c r="AB13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="AE13" t="n">
         <v>16</v>
       </c>
       <c r="AF13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.444</v>
+        <v>0.421</v>
       </c>
       <c r="AH13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI13" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.353</v>
+        <v>0.342</v>
       </c>
       <c r="AK13" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="AL13" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.398</v>
+        <v>0.413</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>624:20</t>
+          <t>660:46</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>267.96</v>
+        <v>283.72</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.543</v>
+        <v>0.55</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.597</v>
+        <v>0.604</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.037</v>
+        <v>1.054</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.131</v>
+        <v>0.127</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.256</v>
+        <v>0.259</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.257</v>
+        <v>1.25</v>
       </c>
       <c r="AV13" t="n">
         <v>0.192</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="14">
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
         <v>43</v>
@@ -2522,7 +2522,7 @@
         <v>0.038</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="15">
@@ -2532,61 +2532,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C15" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F15" t="n">
+        <v>34</v>
+      </c>
+      <c r="G15" t="n">
+        <v>128</v>
+      </c>
+      <c r="H15" t="n">
         <v>33</v>
       </c>
-      <c r="G15" t="n">
-        <v>123</v>
-      </c>
-      <c r="H15" t="n">
-        <v>31</v>
-      </c>
       <c r="I15" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J15" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K15" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R15" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="S15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T15" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="U15" t="n">
         <v>13</v>
@@ -2601,31 +2601,31 @@
         <v>7</v>
       </c>
       <c r="Y15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Z15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.881</v>
+        <v>0.886</v>
       </c>
       <c r="AB15" t="n">
         <v>11</v>
       </c>
       <c r="AC15" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.367</v>
+        <v>0.355</v>
       </c>
       <c r="AE15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.25</v>
+        <v>0.263</v>
       </c>
       <c r="AH15" t="n">
         <v>5</v>
@@ -2637,51 +2637,51 @@
         <v>0.417</v>
       </c>
       <c r="AK15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL15" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.252</v>
+        <v>0.25</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>441:48</t>
+          <t>474:43</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>217.4</v>
+        <v>229.28</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.401</v>
+        <v>0.395</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.449</v>
+        <v>0.445</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.791</v>
+        <v>0.781</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.12</v>
+        <v>0.122</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.176</v>
+        <v>0.178</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.538</v>
+        <v>2.464</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.22</v>
+        <v>0.216</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.034</v>
+        <v>0.036</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.115</v>
+        <v>0.112</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.073</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -2691,37 +2691,37 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16" t="n">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="D16" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E16" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="F16" t="n">
+        <v>74</v>
+      </c>
+      <c r="G16" t="n">
+        <v>201</v>
+      </c>
+      <c r="H16" t="n">
         <v>71</v>
       </c>
-      <c r="G16" t="n">
-        <v>192</v>
-      </c>
-      <c r="H16" t="n">
-        <v>68</v>
-      </c>
       <c r="I16" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J16" t="n">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="K16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M16" t="n">
         <v>26</v>
@@ -2733,25 +2733,25 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="Q16" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="R16" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="S16" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="T16" t="n">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="U16" t="n">
         <v>56</v>
       </c>
       <c r="V16" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="W16" t="n">
         <v>14</v>
@@ -2760,31 +2760,31 @@
         <v>8</v>
       </c>
       <c r="Y16" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="Z16" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AA16" t="n">
         <v>0.744</v>
       </c>
       <c r="AB16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC16" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.489</v>
+        <v>0.48</v>
       </c>
       <c r="AE16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF16" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="AH16" t="n">
         <v>10</v>
@@ -2796,51 +2796,51 @@
         <v>0.556</v>
       </c>
       <c r="AK16" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="AL16" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>822:36</t>
+          <t>869:48</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>467.96</v>
+        <v>496.28</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.501</v>
+        <v>0.496</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.541</v>
+        <v>0.536</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.908</v>
+        <v>0.893</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.16</v>
+        <v>0.167</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.191</v>
+        <v>0.189</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.2</v>
+        <v>2.084</v>
       </c>
       <c r="AV16" t="n">
         <v>0.255</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.075</v>
+        <v>0.074</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.204</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="17">
@@ -2850,67 +2850,67 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C17" t="n">
-        <v>346</v>
+        <v>375</v>
       </c>
       <c r="D17" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E17" t="n">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G17" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H17" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I17" t="n">
+        <v>104</v>
+      </c>
+      <c r="J17" t="n">
+        <v>39</v>
+      </c>
+      <c r="K17" t="n">
+        <v>131</v>
+      </c>
+      <c r="L17" t="n">
+        <v>78</v>
+      </c>
+      <c r="M17" t="n">
+        <v>22</v>
+      </c>
+      <c r="N17" t="n">
+        <v>21</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>47</v>
+      </c>
+      <c r="R17" t="n">
+        <v>107</v>
+      </c>
+      <c r="S17" t="n">
         <v>95</v>
       </c>
-      <c r="J17" t="n">
-        <v>37</v>
-      </c>
-      <c r="K17" t="n">
-        <v>122</v>
-      </c>
-      <c r="L17" t="n">
-        <v>65</v>
-      </c>
-      <c r="M17" t="n">
-        <v>20</v>
-      </c>
-      <c r="N17" t="n">
-        <v>20</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>45</v>
-      </c>
-      <c r="R17" t="n">
-        <v>101</v>
-      </c>
-      <c r="S17" t="n">
-        <v>87</v>
-      </c>
       <c r="T17" t="n">
-        <v>451</v>
+        <v>491</v>
       </c>
       <c r="U17" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="V17" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="W17" t="n">
         <v>21</v>
@@ -2919,31 +2919,31 @@
         <v>12</v>
       </c>
       <c r="Y17" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="Z17" t="n">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.833</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AB17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC17" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.517</v>
       </c>
       <c r="AE17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF17" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.515</v>
+        <v>0.486</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
@@ -2955,48 +2955,48 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AL17" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.385</v>
+        <v>0.404</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>683:20</t>
+          <t>731:40</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>292.8</v>
+        <v>320.76</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.655</v>
+        <v>0.647</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.698</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.182</v>
+        <v>1.169</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.154</v>
+        <v>0.147</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.369</v>
+        <v>0.351</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.822</v>
+        <v>0.83</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.192</v>
+        <v>0.196</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.102</v>
+        <v>0.113</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.196</v>
+        <v>0.198</v>
       </c>
       <c r="AY17" t="n">
         <v>0.045</v>
@@ -3009,67 +3009,67 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M18" t="n">
         <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W18" t="n">
         <v>2</v>
@@ -3078,28 +3078,28 @@
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.8</v>
+        <v>0.778</v>
       </c>
       <c r="AB18" t="n">
         <v>3</v>
       </c>
       <c r="AC18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.333</v>
+        <v>0.231</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -3117,48 +3117,48 @@
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>68:52</t>
+          <t>84:56</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>36.16</v>
+        <v>45.04</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.542</v>
+        <v>0.419</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.597</v>
+        <v>0.486</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.996</v>
+        <v>0.821</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.166</v>
+        <v>0.155</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.417</v>
+        <v>0.355</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.167</v>
+        <v>0.286</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.235</v>
+        <v>0.237</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.078</v>
+        <v>0.1</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.208</v>
+        <v>0.195</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="19">
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.215</v>
+        <v>0.216</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C21" t="n">
         <v>8</v>
@@ -3513,7 +3513,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
         <v>4</v>
@@ -3540,7 +3540,7 @@
         <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>46:17</t>
+          <t>48:28</t>
         </is>
       </c>
       <c r="AO21" t="n">
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.114</v>
+        <v>0.108</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.093</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.024</v>
+        <v>0.046</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
@@ -3645,40 +3645,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D22" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E22" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H22" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I22" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J22" t="n">
         <v>22</v>
       </c>
       <c r="K22" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="L22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N22" t="n">
         <v>13</v>
@@ -3687,19 +3687,19 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R22" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="S22" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="T22" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="U22" t="n">
         <v>17</v>
@@ -3714,87 +3714,87 @@
         <v>9</v>
       </c>
       <c r="Y22" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="Z22" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.773</v>
+        <v>0.75</v>
       </c>
       <c r="AB22" t="n">
         <v>13</v>
       </c>
       <c r="AC22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.433</v>
+        <v>0.406</v>
       </c>
       <c r="AE22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AH22" t="n">
         <v>4</v>
       </c>
       <c r="AI22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.444</v>
+        <v>0.364</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AM22" t="n">
         <v>0</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>361:48</t>
+          <t>401:44</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>141.76</v>
+        <v>158.52</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.536</v>
+        <v>0.505</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.592</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.009</v>
+        <v>0.965</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.148</v>
+        <v>0.139</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.402</v>
+        <v>0.369</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.048</v>
+        <v>1</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.175</v>
+        <v>0.176</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.056</v>
+        <v>0.055</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.188</v>
+        <v>0.182</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="23">
@@ -3947,13 +3947,13 @@
         <v>0.125</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.066</v>
+        <v>0.065</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.142</v>
+        <v>0.143</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.043</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="24">
@@ -3963,16 +3963,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C24" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D24" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E24" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3981,19 +3981,19 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I24" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K24" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L24" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M24" t="n">
         <v>6</v>
@@ -4011,13 +4011,13 @@
         <v>30</v>
       </c>
       <c r="R24" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="S24" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="T24" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="U24" t="n">
         <v>26</v>
@@ -4026,90 +4026,90 @@
         <v>36</v>
       </c>
       <c r="W24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="X24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y24" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="Z24" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.644</v>
+        <v>0.652</v>
       </c>
       <c r="AB24" t="n">
         <v>31</v>
       </c>
       <c r="AC24" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.585</v>
+        <v>0.574</v>
       </c>
       <c r="AE24" t="n">
         <v>8</v>
       </c>
       <c r="AF24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG24" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>362:25</t>
+        </is>
+      </c>
+      <c r="AO24" t="n">
+        <v>196.88</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.056</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="AU24" t="n">
         <v>0.4</v>
       </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>351:41</t>
-        </is>
-      </c>
-      <c r="AO24" t="n">
-        <v>193</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0.626</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.057</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0.338</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0.367</v>
-      </c>
       <c r="AV24" t="n">
-        <v>0.246</v>
+        <v>0.243</v>
       </c>
       <c r="AW24" t="n">
         <v>0.134</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.156</v>
+        <v>0.159</v>
       </c>
       <c r="AY24" t="n">
         <v>0.013</v>
@@ -4122,22 +4122,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C25" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="D25" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E25" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F25" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G25" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="H25" t="n">
         <v>18</v>
@@ -4146,16 +4146,16 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K25" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="L25" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N25" t="n">
         <v>18</v>
@@ -4164,31 +4164,31 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="R25" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="S25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T25" t="n">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="U25" t="n">
         <v>18</v>
       </c>
       <c r="V25" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="W25" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="X25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y25" t="n">
         <v>29</v>
@@ -4209,57 +4209,57 @@
         <v>0.556</v>
       </c>
       <c r="AE25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF25" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.4</v>
+        <v>0.379</v>
       </c>
       <c r="AH25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI25" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
       <c r="AK25" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AL25" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.281</v>
+        <v>0.328</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>537:17</t>
+          <t>580:21</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>173.8</v>
+        <v>187.8</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.497</v>
+        <v>0.516</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.526</v>
+        <v>0.542</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.961</v>
+        <v>0.98</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.096</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.12</v>
+        <v>0.112</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.267</v>
+        <v>1.944</v>
       </c>
       <c r="AV25" t="n">
         <v>0.145</v>
@@ -4268,10 +4268,10 @@
         <v>0.04</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.141</v>
+        <v>0.143</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="26">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -4308,10 +4308,10 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L26" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -4323,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4440,153 +4440,153 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C27" t="n">
-        <v>2751</v>
+        <v>2913</v>
       </c>
       <c r="D27" t="n">
-        <v>603</v>
+        <v>633</v>
       </c>
       <c r="E27" t="n">
-        <v>1105</v>
+        <v>1184</v>
       </c>
       <c r="F27" t="n">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="G27" t="n">
-        <v>1028</v>
+        <v>1097</v>
       </c>
       <c r="H27" t="n">
-        <v>498</v>
+        <v>522</v>
       </c>
       <c r="I27" t="n">
-        <v>657</v>
+        <v>691</v>
       </c>
       <c r="J27" t="n">
-        <v>581</v>
+        <v>610</v>
       </c>
       <c r="K27" t="n">
-        <v>816</v>
+        <v>865</v>
       </c>
       <c r="L27" t="n">
-        <v>383</v>
+        <v>423</v>
       </c>
       <c r="M27" t="n">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="N27" t="n">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>460</v>
+        <v>482</v>
       </c>
       <c r="Q27" t="n">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="R27" t="n">
-        <v>779</v>
+        <v>827</v>
       </c>
       <c r="S27" t="n">
-        <v>681</v>
+        <v>725</v>
       </c>
       <c r="T27" t="n">
-        <v>2976</v>
+        <v>3147</v>
       </c>
       <c r="U27" t="n">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="V27" t="n">
-        <v>360</v>
+        <v>393</v>
       </c>
       <c r="W27" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="X27" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="Y27" t="n">
-        <v>785</v>
+        <v>827</v>
       </c>
       <c r="Z27" t="n">
-        <v>1033</v>
+        <v>1089</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.76</v>
+        <v>0.759</v>
       </c>
       <c r="AB27" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="AC27" t="n">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.475</v>
+        <v>0.459</v>
       </c>
       <c r="AE27" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="AF27" t="n">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.38</v>
+        <v>0.366</v>
       </c>
       <c r="AH27" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AI27" t="n">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.371</v>
+        <v>0.362</v>
       </c>
       <c r="AK27" t="n">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="AL27" t="n">
-        <v>831</v>
+        <v>887</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.332</v>
+        <v>0.337</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>6450:00</t>
+          <t>6850:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>2882.08</v>
+        <v>3067.04</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.528</v>
+        <v>0.524</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.955</v>
+        <v>0.95</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.16</v>
+        <v>0.157</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.233</v>
+        <v>0.229</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.263</v>
+        <v>1.266</v>
       </c>
       <c r="AV27" t="n">
         <v>0.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.064</v>
+        <v>0.065</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.139</v>
+        <v>0.14</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -4599,126 +4599,126 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C28" t="n">
-        <v>2861</v>
+        <v>3024</v>
       </c>
       <c r="D28" t="n">
-        <v>573</v>
+        <v>604</v>
       </c>
       <c r="E28" t="n">
-        <v>1060</v>
+        <v>1106</v>
       </c>
       <c r="F28" t="n">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="G28" t="n">
-        <v>1013</v>
+        <v>1084</v>
       </c>
       <c r="H28" t="n">
-        <v>647</v>
+        <v>685</v>
       </c>
       <c r="I28" t="n">
-        <v>823</v>
+        <v>877</v>
       </c>
       <c r="J28" t="n">
-        <v>580</v>
+        <v>614</v>
       </c>
       <c r="K28" t="n">
-        <v>818</v>
+        <v>871</v>
       </c>
       <c r="L28" t="n">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="M28" t="n">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="N28" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>430</v>
+        <v>456</v>
       </c>
       <c r="Q28" t="n">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="R28" t="n">
-        <v>693</v>
+        <v>737</v>
       </c>
       <c r="S28" t="n">
-        <v>768</v>
+        <v>816</v>
       </c>
       <c r="T28" t="n">
-        <v>3335</v>
+        <v>3519</v>
       </c>
       <c r="U28" t="n">
-        <v>401</v>
+        <v>426</v>
       </c>
       <c r="V28" t="n">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="W28" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="X28" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="Y28" t="n">
-        <v>936</v>
+        <v>992</v>
       </c>
       <c r="Z28" t="n">
-        <v>1198</v>
+        <v>1271</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="AB28" t="n">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="AC28" t="n">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.453</v>
+        <v>0.458</v>
       </c>
       <c r="AE28" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AF28" t="n">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="AG28" t="n">
         <v>0.351</v>
       </c>
       <c r="AH28" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="AI28" t="n">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="AJ28" t="n">
         <v>0.347</v>
       </c>
       <c r="AK28" t="n">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="AL28" t="n">
-        <v>728</v>
+        <v>776</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.353</v>
+        <v>0.348</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>6450:00</t>
+          <t>6850:00</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>2865.12</v>
+        <v>3031.88</v>
       </c>
       <c r="AP28" t="n">
         <v>0.534</v>
@@ -4727,25 +4727,25 @@
         <v>0.587</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.999</v>
+        <v>0.997</v>
       </c>
       <c r="AS28" t="n">
         <v>0.15</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.312</v>
+        <v>0.313</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.349</v>
+        <v>1.346</v>
       </c>
       <c r="AV28" t="n">
         <v>0.2</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.136</v>
+        <v>0.135</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.255</v>
+        <v>0.254</v>
       </c>
       <c r="AW30" t="n">
         <v>0</v>
@@ -4974,156 +4974,156 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>9.875</v>
+        <v>9.441000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>2.281</v>
+        <v>2.147</v>
       </c>
       <c r="E31" t="n">
-        <v>4.031</v>
+        <v>3.882</v>
       </c>
       <c r="F31" t="n">
-        <v>1.312</v>
+        <v>1.265</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>3.941</v>
       </c>
       <c r="H31" t="n">
-        <v>1.375</v>
+        <v>1.353</v>
       </c>
       <c r="I31" t="n">
-        <v>2.375</v>
+        <v>2.353</v>
       </c>
       <c r="J31" t="n">
-        <v>1.031</v>
+        <v>1.059</v>
       </c>
       <c r="K31" t="n">
-        <v>3.312</v>
+        <v>3.471</v>
       </c>
       <c r="L31" t="n">
-        <v>1.094</v>
+        <v>1.147</v>
       </c>
       <c r="M31" t="n">
-        <v>0.75</v>
+        <v>0.735</v>
       </c>
       <c r="N31" t="n">
-        <v>0.719</v>
+        <v>0.706</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.531</v>
+        <v>1.441</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.531</v>
+        <v>1.441</v>
       </c>
       <c r="R31" t="n">
-        <v>2.219</v>
+        <v>2.265</v>
       </c>
       <c r="S31" t="n">
-        <v>2.531</v>
+        <v>2.529</v>
       </c>
       <c r="T31" t="n">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="U31" t="n">
-        <v>1.125</v>
+        <v>1.088</v>
       </c>
       <c r="V31" t="n">
-        <v>1.281</v>
+        <v>1.206</v>
       </c>
       <c r="W31" t="n">
-        <v>0.844</v>
+        <v>0.794</v>
       </c>
       <c r="X31" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.469</v>
+        <v>2.382</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.969</v>
+        <v>3.853</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.622</v>
+        <v>0.618</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.75</v>
+        <v>0.706</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.344</v>
+        <v>1.353</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.522</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.438</v>
+        <v>0.412</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.094</v>
+        <v>1.029</v>
       </c>
       <c r="AG31" t="n">
         <v>0.4</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.781</v>
+        <v>0.794</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.32</v>
+        <v>0.296</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.062</v>
+        <v>1.029</v>
       </c>
       <c r="AL31" t="n">
-        <v>3.219</v>
+        <v>3.147</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.33</v>
+        <v>0.327</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>23:41</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>10.607</v>
+        <v>10.3</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.529</v>
+        <v>0.517</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.544</v>
+        <v>0.533</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.931</v>
+        <v>0.917</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.144</v>
+        <v>0.14</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.171</v>
+        <v>0.173</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.673</v>
+        <v>0.735</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.199</v>
+        <v>0.194</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.049</v>
+        <v>0.051</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.152</v>
+        <v>0.162</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="32">
@@ -5133,156 +5133,156 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C32" t="n">
-        <v>9.781000000000001</v>
+        <v>10.088</v>
       </c>
       <c r="D32" t="n">
-        <v>1.188</v>
+        <v>1.235</v>
       </c>
       <c r="E32" t="n">
-        <v>3.031</v>
+        <v>3.059</v>
       </c>
       <c r="F32" t="n">
-        <v>2.125</v>
+        <v>2.206</v>
       </c>
       <c r="G32" t="n">
-        <v>4.719</v>
+        <v>5</v>
       </c>
       <c r="H32" t="n">
-        <v>1.031</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>1.062</v>
+        <v>1.029</v>
       </c>
       <c r="J32" t="n">
-        <v>2.625</v>
+        <v>2.676</v>
       </c>
       <c r="K32" t="n">
-        <v>1.219</v>
+        <v>1.147</v>
       </c>
       <c r="L32" t="n">
-        <v>0.875</v>
+        <v>0.912</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>0.344</v>
+        <v>0.353</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.094</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.094</v>
+        <v>2</v>
       </c>
       <c r="R32" t="n">
-        <v>3.188</v>
+        <v>3.235</v>
       </c>
       <c r="S32" t="n">
-        <v>2.031</v>
+        <v>2.088</v>
       </c>
       <c r="T32" t="n">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="U32" t="n">
-        <v>1.5</v>
+        <v>1.412</v>
       </c>
       <c r="V32" t="n">
-        <v>1.438</v>
+        <v>1.441</v>
       </c>
       <c r="W32" t="n">
-        <v>0.375</v>
+        <v>0.441</v>
       </c>
       <c r="X32" t="n">
-        <v>0.219</v>
+        <v>0.265</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.531</v>
+        <v>1.588</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.719</v>
+        <v>1.765</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.891</v>
+        <v>0.9</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.406</v>
+        <v>0.382</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.094</v>
+        <v>1.029</v>
       </c>
       <c r="AD32" t="n">
         <v>0.371</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.281</v>
+        <v>0.265</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.281</v>
+        <v>1.294</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.22</v>
+        <v>0.205</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.375</v>
+        <v>0.382</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.75</v>
+        <v>0.765</v>
       </c>
       <c r="AJ32" t="n">
         <v>0.5</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.75</v>
+        <v>1.824</v>
       </c>
       <c r="AL32" t="n">
-        <v>3.969</v>
+        <v>4.235</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.441</v>
+        <v>0.431</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>21:33</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>10.311</v>
+        <v>10.512</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.595</v>
+        <v>0.593</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.949</v>
+        <v>0.96</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.203</v>
+        <v>0.19</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.133</v>
+        <v>0.124</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.254</v>
+        <v>1.338</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.214</v>
+        <v>0.215</v>
       </c>
       <c r="AW32" t="n">
         <v>0.044</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.062</v>
+        <v>0.058</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.099</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="33">
@@ -5292,156 +5292,156 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C33" t="n">
-        <v>7.125</v>
+        <v>7.7</v>
       </c>
       <c r="D33" t="n">
-        <v>2.125</v>
+        <v>2.4</v>
       </c>
       <c r="E33" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="F33" t="n">
-        <v>0.125</v>
+        <v>0.2</v>
       </c>
       <c r="G33" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="H33" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="I33" t="n">
-        <v>3.125</v>
+        <v>2.8</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>1.125</v>
+        <v>1.1</v>
       </c>
       <c r="L33" t="n">
-        <v>0.625</v>
+        <v>0.6</v>
       </c>
       <c r="M33" t="n">
-        <v>0.625</v>
+        <v>0.6</v>
       </c>
       <c r="N33" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="S33" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="T33" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="U33" t="n">
-        <v>1.125</v>
+        <v>1.1</v>
       </c>
       <c r="V33" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="W33" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="X33" t="n">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="Y33" t="n">
-        <v>3.625</v>
+        <v>3.7</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.625</v>
+        <v>4.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.784</v>
+        <v>0.822</v>
       </c>
       <c r="AB33" t="n">
         <v>1</v>
       </c>
       <c r="AC33" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD33" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AM33" t="n">
         <v>0.25</v>
       </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0.167</v>
-      </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>8.125</v>
+        <v>8.332000000000001</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.462</v>
+        <v>0.491</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.572</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.877</v>
+        <v>0.924</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.215</v>
+        <v>0.192</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.5</v>
+        <v>0.418</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.571</v>
+        <v>0.625</v>
       </c>
       <c r="AV33" t="n">
         <v>0.265</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.049</v>
+        <v>0.045</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.09</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.036</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="34">
@@ -5594,7 +5594,7 @@
         <v>0.161</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="AX34" t="n">
         <v>0.154</v>
@@ -5610,156 +5610,156 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>8.688000000000001</v>
+        <v>8.794</v>
       </c>
       <c r="D35" t="n">
-        <v>1.125</v>
+        <v>1.088</v>
       </c>
       <c r="E35" t="n">
-        <v>2.344</v>
+        <v>2.294</v>
       </c>
       <c r="F35" t="n">
-        <v>1.594</v>
+        <v>1.647</v>
       </c>
       <c r="G35" t="n">
-        <v>4.125</v>
+        <v>4.176</v>
       </c>
       <c r="H35" t="n">
-        <v>1.656</v>
+        <v>1.676</v>
       </c>
       <c r="I35" t="n">
-        <v>1.844</v>
+        <v>1.853</v>
       </c>
       <c r="J35" t="n">
-        <v>1.375</v>
+        <v>1.324</v>
       </c>
       <c r="K35" t="n">
-        <v>1.938</v>
+        <v>1.882</v>
       </c>
       <c r="L35" t="n">
-        <v>0.844</v>
+        <v>0.824</v>
       </c>
       <c r="M35" t="n">
-        <v>0.656</v>
+        <v>0.618</v>
       </c>
       <c r="N35" t="n">
-        <v>0.25</v>
+        <v>0.294</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.094</v>
+        <v>1.059</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.094</v>
+        <v>1.059</v>
       </c>
       <c r="R35" t="n">
-        <v>2.156</v>
+        <v>2.118</v>
       </c>
       <c r="S35" t="n">
-        <v>1.438</v>
+        <v>1.5</v>
       </c>
       <c r="T35" t="n">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="U35" t="n">
-        <v>1.125</v>
+        <v>1.147</v>
       </c>
       <c r="V35" t="n">
-        <v>0.531</v>
+        <v>0.5</v>
       </c>
       <c r="W35" t="n">
-        <v>0.719</v>
+        <v>0.676</v>
       </c>
       <c r="X35" t="n">
-        <v>0.469</v>
+        <v>0.441</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.094</v>
+        <v>2.088</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.438</v>
+        <v>2.412</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.859</v>
+        <v>0.866</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.188</v>
+        <v>0.206</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.625</v>
+        <v>0.618</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.125</v>
+        <v>1.118</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.444</v>
+        <v>0.421</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.375</v>
+        <v>0.382</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.062</v>
+        <v>1.118</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.353</v>
+        <v>0.342</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.219</v>
+        <v>1.265</v>
       </c>
       <c r="AL35" t="n">
-        <v>3.062</v>
+        <v>3.059</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.398</v>
+        <v>0.413</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>8.374000000000001</v>
+        <v>8.345000000000001</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.543</v>
+        <v>0.55</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.597</v>
+        <v>0.604</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.037</v>
+        <v>1.054</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.131</v>
+        <v>0.127</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.256</v>
+        <v>0.259</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.257</v>
+        <v>1.25</v>
       </c>
       <c r="AV35" t="n">
         <v>0.192</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="36">
@@ -5769,126 +5769,126 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C36" t="n">
-        <v>1.344</v>
+        <v>1.265</v>
       </c>
       <c r="D36" t="n">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
       <c r="E36" t="n">
-        <v>0.281</v>
+        <v>0.265</v>
       </c>
       <c r="F36" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="G36" t="n">
-        <v>1.094</v>
+        <v>1.029</v>
       </c>
       <c r="H36" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="I36" t="n">
-        <v>0.438</v>
+        <v>0.412</v>
       </c>
       <c r="J36" t="n">
-        <v>1.062</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="L36" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="M36" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.656</v>
+        <v>0.618</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.656</v>
+        <v>0.618</v>
       </c>
       <c r="R36" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="S36" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="T36" t="n">
         <v>39</v>
       </c>
       <c r="U36" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="V36" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="W36" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="X36" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.469</v>
+        <v>0.441</v>
       </c>
       <c r="AA36" t="n">
         <v>0.8</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AD36" t="n">
         <v>0.333</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="AG36" t="n">
         <v>0.4</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="AJ36" t="n">
         <v>0.2</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.882</v>
       </c>
       <c r="AM36" t="n">
         <v>0.233</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>05:24</t>
+          <t>05:05</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>2.224</v>
+        <v>2.093</v>
       </c>
       <c r="AP36" t="n">
         <v>0.364</v>
@@ -5918,7 +5918,7 @@
         <v>0.038</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="37">
@@ -5928,156 +5928,156 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C37" t="n">
-        <v>5.375</v>
+        <v>5.265</v>
       </c>
       <c r="D37" t="n">
-        <v>0.656</v>
+        <v>0.647</v>
       </c>
       <c r="E37" t="n">
-        <v>1.656</v>
+        <v>1.676</v>
       </c>
       <c r="F37" t="n">
-        <v>1.031</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>3.844</v>
+        <v>3.765</v>
       </c>
       <c r="H37" t="n">
-        <v>0.969</v>
+        <v>0.971</v>
       </c>
       <c r="I37" t="n">
-        <v>1.094</v>
+        <v>1.088</v>
       </c>
       <c r="J37" t="n">
-        <v>2.062</v>
+        <v>2.029</v>
       </c>
       <c r="K37" t="n">
-        <v>1.438</v>
+        <v>1.412</v>
       </c>
       <c r="L37" t="n">
-        <v>0.438</v>
+        <v>0.471</v>
       </c>
       <c r="M37" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.588</v>
       </c>
       <c r="N37" t="n">
-        <v>0.188</v>
+        <v>0.206</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.824</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.824</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>1.059</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="U37" t="n">
-        <v>0.406</v>
+        <v>0.382</v>
       </c>
       <c r="V37" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="W37" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="X37" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.156</v>
+        <v>1.147</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.312</v>
+        <v>1.294</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.881</v>
+        <v>0.886</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.912</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.367</v>
+        <v>0.355</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.125</v>
+        <v>0.147</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.5</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.25</v>
+        <v>0.263</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="AJ37" t="n">
         <v>0.417</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.875</v>
+        <v>0.853</v>
       </c>
       <c r="AL37" t="n">
-        <v>3.469</v>
+        <v>3.412</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.252</v>
+        <v>0.25</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>6.794</v>
+        <v>6.744</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.401</v>
+        <v>0.395</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.449</v>
+        <v>0.445</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.791</v>
+        <v>0.781</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.12</v>
+        <v>0.122</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.176</v>
+        <v>0.178</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.538</v>
+        <v>2.464</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.22</v>
+        <v>0.216</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.034</v>
+        <v>0.036</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.115</v>
+        <v>0.112</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.073</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -6087,156 +6087,156 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C38" t="n">
-        <v>13.281</v>
+        <v>13.029</v>
       </c>
       <c r="D38" t="n">
-        <v>2.25</v>
+        <v>2.206</v>
       </c>
       <c r="E38" t="n">
-        <v>5.125</v>
+        <v>5.118</v>
       </c>
       <c r="F38" t="n">
-        <v>2.219</v>
+        <v>2.176</v>
       </c>
       <c r="G38" t="n">
-        <v>6</v>
+        <v>5.912</v>
       </c>
       <c r="H38" t="n">
-        <v>2.125</v>
+        <v>2.088</v>
       </c>
       <c r="I38" t="n">
-        <v>2.625</v>
+        <v>2.559</v>
       </c>
       <c r="J38" t="n">
-        <v>5.156</v>
+        <v>5.088</v>
       </c>
       <c r="K38" t="n">
-        <v>1.75</v>
+        <v>1.706</v>
       </c>
       <c r="L38" t="n">
-        <v>0.594</v>
+        <v>0.647</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.765</v>
       </c>
       <c r="N38" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.344</v>
+        <v>2.441</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.344</v>
+        <v>2.441</v>
       </c>
       <c r="R38" t="n">
-        <v>1.688</v>
+        <v>1.706</v>
       </c>
       <c r="S38" t="n">
-        <v>3.344</v>
+        <v>3.265</v>
       </c>
       <c r="T38" t="n">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="U38" t="n">
-        <v>1.75</v>
+        <v>1.647</v>
       </c>
       <c r="V38" t="n">
-        <v>1.594</v>
+        <v>1.647</v>
       </c>
       <c r="W38" t="n">
-        <v>0.438</v>
+        <v>0.412</v>
       </c>
       <c r="X38" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.719</v>
+        <v>2.647</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.656</v>
+        <v>3.559</v>
       </c>
       <c r="AA38" t="n">
         <v>0.744</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.719</v>
+        <v>0.706</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.469</v>
+        <v>1.471</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.489</v>
+        <v>0.48</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.625</v>
+        <v>2.647</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.312</v>
+        <v>0.294</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="AJ38" t="n">
         <v>0.556</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.906</v>
+        <v>1.882</v>
       </c>
       <c r="AL38" t="n">
-        <v>5.438</v>
+        <v>5.382</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>25:42</t>
+          <t>25:34</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>14.624</v>
+        <v>14.596</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.501</v>
+        <v>0.496</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.541</v>
+        <v>0.536</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.908</v>
+        <v>0.893</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.16</v>
+        <v>0.167</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.191</v>
+        <v>0.189</v>
       </c>
       <c r="AU38" t="n">
-        <v>2.2</v>
+        <v>2.084</v>
       </c>
       <c r="AV38" t="n">
         <v>0.255</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.075</v>
+        <v>0.074</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.204</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="39">
@@ -6246,153 +6246,153 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C39" t="n">
-        <v>10.812</v>
+        <v>11.029</v>
       </c>
       <c r="D39" t="n">
-        <v>3.281</v>
+        <v>3.324</v>
       </c>
       <c r="E39" t="n">
-        <v>4.75</v>
+        <v>4.971</v>
       </c>
       <c r="F39" t="n">
-        <v>0.625</v>
+        <v>0.676</v>
       </c>
       <c r="G39" t="n">
-        <v>1.688</v>
+        <v>1.735</v>
       </c>
       <c r="H39" t="n">
-        <v>2.375</v>
+        <v>2.353</v>
       </c>
       <c r="I39" t="n">
-        <v>2.969</v>
+        <v>3.059</v>
       </c>
       <c r="J39" t="n">
-        <v>1.156</v>
+        <v>1.147</v>
       </c>
       <c r="K39" t="n">
-        <v>3.812</v>
+        <v>3.853</v>
       </c>
       <c r="L39" t="n">
-        <v>2.031</v>
+        <v>2.294</v>
       </c>
       <c r="M39" t="n">
-        <v>0.625</v>
+        <v>0.647</v>
       </c>
       <c r="N39" t="n">
-        <v>0.625</v>
+        <v>0.618</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.406</v>
+        <v>1.382</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.406</v>
+        <v>1.382</v>
       </c>
       <c r="R39" t="n">
-        <v>3.156</v>
+        <v>3.147</v>
       </c>
       <c r="S39" t="n">
-        <v>2.719</v>
+        <v>2.794</v>
       </c>
       <c r="T39" t="n">
-        <v>451</v>
+        <v>491</v>
       </c>
       <c r="U39" t="n">
-        <v>0.844</v>
+        <v>0.853</v>
       </c>
       <c r="V39" t="n">
-        <v>2.094</v>
+        <v>2.294</v>
       </c>
       <c r="W39" t="n">
-        <v>0.656</v>
+        <v>0.618</v>
       </c>
       <c r="X39" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="Y39" t="n">
-        <v>4.219</v>
+        <v>4.265</v>
       </c>
       <c r="Z39" t="n">
-        <v>5.062</v>
+        <v>5.235</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.833</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.906</v>
+        <v>0.882</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.625</v>
+        <v>1.706</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.517</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.531</v>
+        <v>0.529</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.031</v>
+        <v>1.088</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.515</v>
+        <v>0.486</v>
       </c>
       <c r="AH39" t="n">
         <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AJ39" t="n">
         <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.625</v>
+        <v>0.676</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.625</v>
+        <v>1.676</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.385</v>
+        <v>0.404</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>9.15</v>
+        <v>9.433999999999999</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.655</v>
+        <v>0.647</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.698</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.182</v>
+        <v>1.169</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.154</v>
+        <v>0.147</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.369</v>
+        <v>0.351</v>
       </c>
       <c r="AU39" t="n">
-        <v>0.822</v>
+        <v>0.83</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.192</v>
+        <v>0.196</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.102</v>
+        <v>0.113</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.196</v>
+        <v>0.198</v>
       </c>
       <c r="AY39" t="n">
         <v>0.045</v>
@@ -6405,98 +6405,98 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C40" t="n">
-        <v>7.2</v>
+        <v>6.167</v>
       </c>
       <c r="D40" t="n">
-        <v>2.6</v>
+        <v>2.167</v>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>4.333</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>2.667</v>
       </c>
       <c r="J40" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="K40" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>1.333</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="N40" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="R40" t="n">
-        <v>3</v>
+        <v>2.667</v>
       </c>
       <c r="S40" t="n">
-        <v>2.6</v>
+        <v>2.333</v>
       </c>
       <c r="T40" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="U40" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="V40" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="W40" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="X40" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="Y40" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.8</v>
+        <v>0.778</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.8</v>
+        <v>2.167</v>
       </c>
       <c r="AD40" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
         <v>0.333</v>
       </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0</v>
-      </c>
       <c r="AG40" t="n">
         <v>0</v>
       </c>
@@ -6513,48 +6513,48 @@
         <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="AM40" t="n">
         <v>0</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>7.232</v>
+        <v>7.507</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.542</v>
+        <v>0.419</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.597</v>
+        <v>0.486</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.996</v>
+        <v>0.821</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.166</v>
+        <v>0.155</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.417</v>
+        <v>0.355</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.167</v>
+        <v>0.286</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.235</v>
+        <v>0.237</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.078</v>
+        <v>0.1</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.208</v>
+        <v>0.195</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="41">
@@ -6869,7 +6869,7 @@
         <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.215</v>
+        <v>0.216</v>
       </c>
       <c r="AY42" t="n">
         <v>0</v>
@@ -6882,37 +6882,37 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C43" t="n">
-        <v>0.889</v>
+        <v>0.727</v>
       </c>
       <c r="D43" t="n">
-        <v>0.111</v>
+        <v>0.091</v>
       </c>
       <c r="E43" t="n">
-        <v>0.222</v>
+        <v>0.182</v>
       </c>
       <c r="F43" t="n">
-        <v>0.111</v>
+        <v>0.091</v>
       </c>
       <c r="G43" t="n">
-        <v>0.556</v>
+        <v>0.455</v>
       </c>
       <c r="H43" t="n">
-        <v>0.333</v>
+        <v>0.273</v>
       </c>
       <c r="I43" t="n">
-        <v>0.444</v>
+        <v>0.364</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0.111</v>
+        <v>0.182</v>
       </c>
       <c r="L43" t="n">
-        <v>0.444</v>
+        <v>0.364</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -6924,25 +6924,25 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.333</v>
+        <v>0.273</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.333</v>
+        <v>0.273</v>
       </c>
       <c r="R43" t="n">
-        <v>0.778</v>
+        <v>0.636</v>
       </c>
       <c r="S43" t="n">
-        <v>0.333</v>
+        <v>0.273</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0.556</v>
+        <v>0.455</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -6951,19 +6951,19 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.333</v>
+        <v>0.273</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.444</v>
+        <v>0.364</v>
       </c>
       <c r="AA43" t="n">
         <v>0.75</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.111</v>
+        <v>0.091</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.111</v>
+        <v>0.091</v>
       </c>
       <c r="AD43" t="n">
         <v>1</v>
@@ -6972,16 +6972,16 @@
         <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.111</v>
+        <v>0.091</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.111</v>
+        <v>0.091</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.222</v>
+        <v>0.182</v>
       </c>
       <c r="AJ43" t="n">
         <v>0.5</v>
@@ -6990,18 +6990,18 @@
         <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.333</v>
+        <v>0.273</v>
       </c>
       <c r="AM43" t="n">
         <v>0</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>05:08</t>
+          <t>04:24</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>1.307</v>
+        <v>1.069</v>
       </c>
       <c r="AP43" t="n">
         <v>0.357</v>
@@ -7022,13 +7022,13 @@
         <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.114</v>
+        <v>0.108</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.093</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.024</v>
+        <v>0.046</v>
       </c>
       <c r="AY43" t="n">
         <v>0</v>
@@ -7041,156 +7041,156 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C44" t="n">
-        <v>7.944</v>
+        <v>7.65</v>
       </c>
       <c r="D44" t="n">
-        <v>2.556</v>
+        <v>2.5</v>
       </c>
       <c r="E44" t="n">
-        <v>3.833</v>
+        <v>3.9</v>
       </c>
       <c r="F44" t="n">
-        <v>0.222</v>
+        <v>0.2</v>
       </c>
       <c r="G44" t="n">
-        <v>1.556</v>
+        <v>1.65</v>
       </c>
       <c r="H44" t="n">
-        <v>2.167</v>
+        <v>2.05</v>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
-        <v>1.222</v>
+        <v>1.1</v>
       </c>
       <c r="K44" t="n">
-        <v>3.444</v>
+        <v>3.3</v>
       </c>
       <c r="L44" t="n">
-        <v>1.056</v>
+        <v>1.05</v>
       </c>
       <c r="M44" t="n">
-        <v>0.556</v>
+        <v>0.55</v>
       </c>
       <c r="N44" t="n">
-        <v>0.722</v>
+        <v>0.65</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.167</v>
+        <v>1.1</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.167</v>
+        <v>1.1</v>
       </c>
       <c r="R44" t="n">
-        <v>2.833</v>
+        <v>2.75</v>
       </c>
       <c r="S44" t="n">
-        <v>3.333</v>
+        <v>3.35</v>
       </c>
       <c r="T44" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="U44" t="n">
-        <v>0.944</v>
+        <v>0.85</v>
       </c>
       <c r="V44" t="n">
-        <v>1.056</v>
+        <v>0.95</v>
       </c>
       <c r="W44" t="n">
-        <v>0.778</v>
+        <v>0.7</v>
       </c>
       <c r="X44" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="Y44" t="n">
-        <v>3.778</v>
+        <v>3.6</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.889</v>
+        <v>4.8</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.773</v>
+        <v>0.75</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.722</v>
+        <v>0.65</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.667</v>
+        <v>1.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.433</v>
+        <v>0.406</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.222</v>
+        <v>0.3</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.278</v>
+        <v>0.4</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.222</v>
+        <v>0.2</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.444</v>
+        <v>0.364</v>
       </c>
       <c r="AK44" t="n">
         <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.056</v>
+        <v>1.1</v>
       </c>
       <c r="AM44" t="n">
         <v>0</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>7.876</v>
+        <v>7.926</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.536</v>
+        <v>0.505</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.592</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.009</v>
+        <v>0.965</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.148</v>
+        <v>0.139</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.402</v>
+        <v>0.369</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.048</v>
+        <v>1</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.175</v>
+        <v>0.176</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.056</v>
+        <v>0.055</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.188</v>
+        <v>0.182</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.045</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="45">
@@ -7343,10 +7343,10 @@
         <v>0.125</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.066</v>
+        <v>0.065</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.142</v>
+        <v>0.143</v>
       </c>
       <c r="AY45" t="n">
         <v>0.045</v>
@@ -7359,16 +7359,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C46" t="n">
-        <v>7.034</v>
+        <v>6.933</v>
       </c>
       <c r="D46" t="n">
-        <v>2.759</v>
+        <v>2.7</v>
       </c>
       <c r="E46" t="n">
-        <v>4.483</v>
+        <v>4.433</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -7377,138 +7377,138 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.517</v>
+        <v>1.533</v>
       </c>
       <c r="I46" t="n">
-        <v>2.586</v>
+        <v>2.567</v>
       </c>
       <c r="J46" t="n">
-        <v>0.379</v>
+        <v>0.4</v>
       </c>
       <c r="K46" t="n">
-        <v>1.724</v>
+        <v>1.733</v>
       </c>
       <c r="L46" t="n">
-        <v>1.517</v>
+        <v>1.533</v>
       </c>
       <c r="M46" t="n">
-        <v>0.207</v>
+        <v>0.2</v>
       </c>
       <c r="N46" t="n">
-        <v>0.586</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.034</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.034</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>2.793</v>
+        <v>2.833</v>
       </c>
       <c r="S46" t="n">
-        <v>2.241</v>
+        <v>2.233</v>
       </c>
       <c r="T46" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="U46" t="n">
-        <v>0.897</v>
+        <v>0.867</v>
       </c>
       <c r="V46" t="n">
-        <v>1.241</v>
+        <v>1.2</v>
       </c>
       <c r="W46" t="n">
-        <v>0.655</v>
+        <v>0.7</v>
       </c>
       <c r="X46" t="n">
-        <v>0.414</v>
+        <v>0.433</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.931</v>
+        <v>2.933</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.552</v>
+        <v>4.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.644</v>
+        <v>0.652</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.069</v>
+        <v>1.033</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.828</v>
+        <v>1.8</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.585</v>
+        <v>0.574</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.276</v>
+        <v>0.267</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AG46" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AO46" t="n">
+        <v>6.563</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1.056</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="AU46" t="n">
         <v>0.4</v>
       </c>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AO46" t="n">
-        <v>6.655</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>0.626</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>1.057</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>0.338</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>0.367</v>
-      </c>
       <c r="AV46" t="n">
-        <v>0.246</v>
+        <v>0.243</v>
       </c>
       <c r="AW46" t="n">
         <v>0.134</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.156</v>
+        <v>0.159</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="47">
@@ -7518,144 +7518,144 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C47" t="n">
-        <v>5.387</v>
+        <v>5.576</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="E47" t="n">
-        <v>1.774</v>
+        <v>1.788</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9350000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="G47" t="n">
-        <v>3.065</v>
+        <v>3.091</v>
       </c>
       <c r="H47" t="n">
-        <v>0.581</v>
+        <v>0.545</v>
       </c>
       <c r="I47" t="n">
-        <v>0.645</v>
+        <v>0.606</v>
       </c>
       <c r="J47" t="n">
-        <v>1.097</v>
+        <v>1.061</v>
       </c>
       <c r="K47" t="n">
-        <v>2.226</v>
+        <v>2.273</v>
       </c>
       <c r="L47" t="n">
-        <v>0.645</v>
+        <v>0.667</v>
       </c>
       <c r="M47" t="n">
-        <v>0.387</v>
+        <v>0.394</v>
       </c>
       <c r="N47" t="n">
-        <v>0.581</v>
+        <v>0.545</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.484</v>
+        <v>0.545</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.484</v>
+        <v>0.545</v>
       </c>
       <c r="R47" t="n">
-        <v>2.387</v>
+        <v>2.394</v>
       </c>
       <c r="S47" t="n">
-        <v>0.548</v>
+        <v>0.545</v>
       </c>
       <c r="T47" t="n">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="U47" t="n">
-        <v>0.581</v>
+        <v>0.545</v>
       </c>
       <c r="V47" t="n">
-        <v>0.323</v>
+        <v>0.545</v>
       </c>
       <c r="W47" t="n">
-        <v>0.355</v>
+        <v>0.424</v>
       </c>
       <c r="X47" t="n">
-        <v>0.194</v>
+        <v>0.212</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.879</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.032</v>
+        <v>0.97</v>
       </c>
       <c r="AA47" t="n">
         <v>0.906</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.323</v>
+        <v>0.303</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.581</v>
+        <v>0.545</v>
       </c>
       <c r="AD47" t="n">
         <v>0.556</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.323</v>
+        <v>0.333</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.806</v>
+        <v>0.879</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.4</v>
+        <v>0.379</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.419</v>
+        <v>0.424</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.226</v>
+        <v>1.242</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
       <c r="AK47" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="AN47" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AO47" t="n">
+        <v>5.691</v>
+      </c>
+      <c r="AP47" t="n">
         <v>0.516</v>
       </c>
-      <c r="AL47" t="n">
-        <v>1.839</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>0.281</v>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>17:19</t>
-        </is>
-      </c>
-      <c r="AO47" t="n">
-        <v>5.606</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>0.497</v>
-      </c>
       <c r="AQ47" t="n">
-        <v>0.526</v>
+        <v>0.542</v>
       </c>
       <c r="AR47" t="n">
-        <v>0.961</v>
+        <v>0.98</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.096</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.12</v>
+        <v>0.112</v>
       </c>
       <c r="AU47" t="n">
-        <v>2.267</v>
+        <v>1.944</v>
       </c>
       <c r="AV47" t="n">
         <v>0.145</v>
@@ -7664,10 +7664,10 @@
         <v>0.04</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.141</v>
+        <v>0.143</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="48">
@@ -7677,7 +7677,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -7704,10 +7704,10 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1.969</v>
+        <v>2</v>
       </c>
       <c r="L48" t="n">
-        <v>1.344</v>
+        <v>1.382</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -7719,13 +7719,13 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.676</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -7836,153 +7836,153 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C49" t="n">
-        <v>85.96899999999999</v>
+        <v>85.676</v>
       </c>
       <c r="D49" t="n">
-        <v>18.844</v>
+        <v>18.618</v>
       </c>
       <c r="E49" t="n">
-        <v>34.531</v>
+        <v>34.824</v>
       </c>
       <c r="F49" t="n">
-        <v>10.906</v>
+        <v>11.029</v>
       </c>
       <c r="G49" t="n">
-        <v>32.125</v>
+        <v>32.265</v>
       </c>
       <c r="H49" t="n">
-        <v>15.562</v>
+        <v>15.353</v>
       </c>
       <c r="I49" t="n">
-        <v>20.531</v>
+        <v>20.324</v>
       </c>
       <c r="J49" t="n">
-        <v>18.156</v>
+        <v>17.941</v>
       </c>
       <c r="K49" t="n">
-        <v>25.5</v>
+        <v>25.441</v>
       </c>
       <c r="L49" t="n">
-        <v>11.969</v>
+        <v>12.441</v>
       </c>
       <c r="M49" t="n">
-        <v>6.156</v>
+        <v>6.088</v>
       </c>
       <c r="N49" t="n">
-        <v>4.562</v>
+        <v>4.559</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>14.375</v>
+        <v>14.176</v>
       </c>
       <c r="Q49" t="n">
-        <v>13.688</v>
+        <v>13.5</v>
       </c>
       <c r="R49" t="n">
-        <v>24.344</v>
+        <v>24.324</v>
       </c>
       <c r="S49" t="n">
-        <v>21.281</v>
+        <v>21.324</v>
       </c>
       <c r="T49" t="n">
-        <v>2976</v>
+        <v>3147</v>
       </c>
       <c r="U49" t="n">
-        <v>10.031</v>
+        <v>9.676</v>
       </c>
       <c r="V49" t="n">
-        <v>11.25</v>
+        <v>11.559</v>
       </c>
       <c r="W49" t="n">
-        <v>5.938</v>
+        <v>5.824</v>
       </c>
       <c r="X49" t="n">
-        <v>3.438</v>
+        <v>3.353</v>
       </c>
       <c r="Y49" t="n">
-        <v>24.531</v>
+        <v>24.324</v>
       </c>
       <c r="Z49" t="n">
-        <v>32.281</v>
+        <v>32.029</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.76</v>
+        <v>0.759</v>
       </c>
       <c r="AB49" t="n">
-        <v>6.062</v>
+        <v>5.853</v>
       </c>
       <c r="AC49" t="n">
-        <v>12.75</v>
+        <v>12.765</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.475</v>
+        <v>0.459</v>
       </c>
       <c r="AE49" t="n">
-        <v>3.812</v>
+        <v>3.794</v>
       </c>
       <c r="AF49" t="n">
-        <v>10.031</v>
+        <v>10.353</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.38</v>
+        <v>0.366</v>
       </c>
       <c r="AH49" t="n">
-        <v>2.281</v>
+        <v>2.235</v>
       </c>
       <c r="AI49" t="n">
-        <v>6.156</v>
+        <v>6.176</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.371</v>
+        <v>0.362</v>
       </c>
       <c r="AK49" t="n">
-        <v>8.625</v>
+        <v>8.794</v>
       </c>
       <c r="AL49" t="n">
-        <v>25.969</v>
+        <v>26.088</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.332</v>
+        <v>0.337</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>201:33</t>
+          <t>201:28</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>90.065</v>
+        <v>90.20699999999999</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.528</v>
+        <v>0.524</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR49" t="n">
-        <v>0.955</v>
+        <v>0.95</v>
       </c>
       <c r="AS49" t="n">
-        <v>0.16</v>
+        <v>0.157</v>
       </c>
       <c r="AT49" t="n">
-        <v>0.233</v>
+        <v>0.229</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.263</v>
+        <v>1.266</v>
       </c>
       <c r="AV49" t="n">
         <v>0.2</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.064</v>
+        <v>0.065</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.139</v>
+        <v>0.14</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -7995,126 +7995,126 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C50" t="n">
-        <v>89.40600000000001</v>
+        <v>88.941</v>
       </c>
       <c r="D50" t="n">
-        <v>17.906</v>
+        <v>17.765</v>
       </c>
       <c r="E50" t="n">
-        <v>33.125</v>
+        <v>32.529</v>
       </c>
       <c r="F50" t="n">
-        <v>11.125</v>
+        <v>11.088</v>
       </c>
       <c r="G50" t="n">
-        <v>31.656</v>
+        <v>31.882</v>
       </c>
       <c r="H50" t="n">
-        <v>20.219</v>
+        <v>20.147</v>
       </c>
       <c r="I50" t="n">
-        <v>25.719</v>
+        <v>25.794</v>
       </c>
       <c r="J50" t="n">
-        <v>18.125</v>
+        <v>18.059</v>
       </c>
       <c r="K50" t="n">
-        <v>25.562</v>
+        <v>25.618</v>
       </c>
       <c r="L50" t="n">
-        <v>11.156</v>
+        <v>11.029</v>
       </c>
       <c r="M50" t="n">
-        <v>7.719</v>
+        <v>7.559</v>
       </c>
       <c r="N50" t="n">
-        <v>4.594</v>
+        <v>4.588</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>13.438</v>
+        <v>13.412</v>
       </c>
       <c r="Q50" t="n">
-        <v>12.469</v>
+        <v>12.412</v>
       </c>
       <c r="R50" t="n">
-        <v>21.656</v>
+        <v>21.676</v>
       </c>
       <c r="S50" t="n">
         <v>24</v>
       </c>
       <c r="T50" t="n">
-        <v>3335</v>
+        <v>3519</v>
       </c>
       <c r="U50" t="n">
-        <v>12.531</v>
+        <v>12.529</v>
       </c>
       <c r="V50" t="n">
-        <v>10.969</v>
+        <v>10.676</v>
       </c>
       <c r="W50" t="n">
-        <v>6.094</v>
+        <v>6.088</v>
       </c>
       <c r="X50" t="n">
-        <v>4.031</v>
+        <v>3.971</v>
       </c>
       <c r="Y50" t="n">
-        <v>29.25</v>
+        <v>29.176</v>
       </c>
       <c r="Z50" t="n">
-        <v>37.438</v>
+        <v>37.382</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="AB50" t="n">
-        <v>6.031</v>
+        <v>5.941</v>
       </c>
       <c r="AC50" t="n">
-        <v>13.312</v>
+        <v>12.971</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.453</v>
+        <v>0.458</v>
       </c>
       <c r="AE50" t="n">
-        <v>2.844</v>
+        <v>2.794</v>
       </c>
       <c r="AF50" t="n">
-        <v>8.093999999999999</v>
+        <v>7.971</v>
       </c>
       <c r="AG50" t="n">
         <v>0.351</v>
       </c>
       <c r="AH50" t="n">
-        <v>3.094</v>
+        <v>3.147</v>
       </c>
       <c r="AI50" t="n">
-        <v>8.906000000000001</v>
+        <v>9.058999999999999</v>
       </c>
       <c r="AJ50" t="n">
         <v>0.347</v>
       </c>
       <c r="AK50" t="n">
-        <v>8.031000000000001</v>
+        <v>7.941</v>
       </c>
       <c r="AL50" t="n">
-        <v>22.75</v>
+        <v>22.824</v>
       </c>
       <c r="AM50" t="n">
-        <v>0.353</v>
+        <v>0.348</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>201:33</t>
+          <t>201:28</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>89.535</v>
+        <v>89.173</v>
       </c>
       <c r="AP50" t="n">
         <v>0.534</v>
@@ -8123,25 +8123,25 @@
         <v>0.587</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.999</v>
+        <v>0.997</v>
       </c>
       <c r="AS50" t="n">
         <v>0.15</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.312</v>
+        <v>0.313</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.349</v>
+        <v>1.346</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.199</v>
+        <v>0.198</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.059</v>
+        <v>0.058</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.139</v>
+        <v>0.14</v>
       </c>
       <c r="AY50" t="n">
         <v>0</v>
